--- a/Source/arkD.xlsx
+++ b/Source/arkD.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37b141e1e60375e0/Arknights/ArknightsIDcard-Ebranch/ArknightsIDCard/Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{07D95BDE-5E8B-4E78-91B2-53470496501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56467737-4EF0-4B21-B220-FF5896AB707E}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{07D95BDE-5E8B-4E78-91B2-53470496501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B20ECC4-9D76-4ADB-A28D-E5C31030D5EE}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="14620" windowHeight="25220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="其他信息" sheetId="2" r:id="rId1"/>
     <sheet name="练度表" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$269</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="411">
   <si>
     <t>陈</t>
   </si>
@@ -706,716 +706,753 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>HOK-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMB-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晓歌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿米娅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin3</t>
+  </si>
+  <si>
+    <t>阿消</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>崖心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猎蜂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARC-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛恩纳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRO-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野鬃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四五星三技能填0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不填则随机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模组等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗小黑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡泡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗索</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒芒克洛丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>九色鹿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食铁兽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>见行者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海沫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白铁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOL-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伺夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斥罪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缄默德克萨斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贾维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铅踝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUM-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耶拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>焰影苇草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石英</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCR-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火哨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>临光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谜图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仇白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铎铃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉维尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>截云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因陀罗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断罪者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麒麟X夜刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUS-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火龙S黑角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊内丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLX-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRP-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星极</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缪尔赛思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霍尔海雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淬羽赫默</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Castle-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰拉大陆调查团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义骑士号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lancet-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U-Official</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOM-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHY-Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMD-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elite1</t>
+  </si>
+  <si>
+    <t>玫拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普罗旺斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特米米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚雷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗比菈塔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friston-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣约送葬人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEA-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提丰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIE-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒檀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杰西卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THRM-EX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琳琅诗怀雅</t>
+  </si>
+  <si>
+    <t>MER-X</t>
+  </si>
+  <si>
+    <t>CEN-X</t>
+  </si>
+  <si>
+    <t>REA-X</t>
+  </si>
+  <si>
+    <t>纯烬艾雅法拉</t>
+  </si>
+  <si>
+    <t>BEA-X</t>
+  </si>
+  <si>
+    <t>青枳</t>
+  </si>
+  <si>
+    <t>涤火杰西卡</t>
+  </si>
+  <si>
+    <t>冰酿</t>
+  </si>
+  <si>
+    <t>杏仁</t>
+  </si>
+  <si>
+    <t>BLS-X</t>
+  </si>
+  <si>
+    <t>赫德雷</t>
+  </si>
+  <si>
+    <t>FOR-X</t>
+  </si>
+  <si>
+    <t>ARC-X</t>
+  </si>
+  <si>
+    <t>刺玫</t>
+  </si>
+  <si>
+    <t>薇薇安娜</t>
+  </si>
+  <si>
+    <t>止颂</t>
+  </si>
+  <si>
+    <t>UNY-X</t>
+  </si>
+  <si>
+    <t>塑心</t>
+  </si>
+  <si>
+    <t>锏</t>
+  </si>
+  <si>
+    <t>FUN-X</t>
+  </si>
+  <si>
+    <t>INC-X</t>
+  </si>
+  <si>
+    <t>DEC-Y</t>
+  </si>
+  <si>
+    <t>赤冬</t>
+  </si>
+  <si>
+    <t>烈夏</t>
+  </si>
+  <si>
+    <t>摩根</t>
+  </si>
+  <si>
+    <t>凛视</t>
+  </si>
+  <si>
+    <t>跃跃</t>
+  </si>
+  <si>
+    <t>杜宾</t>
+  </si>
+  <si>
+    <t>霜叶</t>
+  </si>
+  <si>
+    <t>莱伊</t>
+  </si>
+  <si>
+    <t>艾丝黛尔</t>
+  </si>
+  <si>
+    <t>FGT-Y</t>
+  </si>
+  <si>
+    <t>FGT-X</t>
+  </si>
+  <si>
+    <t>左乐</t>
+  </si>
+  <si>
+    <t>黍</t>
+  </si>
+  <si>
+    <t>万顷</t>
+  </si>
+  <si>
+    <t>小满</t>
+  </si>
+  <si>
+    <t>SBL-X</t>
+  </si>
+  <si>
+    <t>GUA-X</t>
+  </si>
+  <si>
+    <t>红隼</t>
+  </si>
+  <si>
+    <t>夜烟</t>
+  </si>
+  <si>
+    <t>SPT-X</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>TRP-Δ</t>
+  </si>
+  <si>
+    <t>导火索</t>
+  </si>
+  <si>
+    <t>医生</t>
+  </si>
+  <si>
+    <t>双月</t>
+  </si>
+  <si>
+    <t>芳汀</t>
+  </si>
+  <si>
+    <t>AMB-X</t>
+  </si>
+  <si>
+    <t>杰克</t>
+  </si>
+  <si>
+    <t>酸糖</t>
+  </si>
+  <si>
+    <t>休谟斯</t>
+  </si>
+  <si>
+    <t>INS-Y</t>
+  </si>
+  <si>
+    <t>TAC-X</t>
+  </si>
+  <si>
+    <t>阿斯卡纶</t>
+  </si>
+  <si>
+    <t>LOR-X</t>
+  </si>
+  <si>
+    <t>维什戴尔</t>
+  </si>
+  <si>
+    <t>BOM-X</t>
+  </si>
+  <si>
+    <t>逻各斯</t>
+  </si>
+  <si>
+    <t>魔王</t>
+  </si>
+  <si>
+    <t>CCR-X</t>
+  </si>
+  <si>
+    <t>CCR-Δ</t>
+  </si>
+  <si>
+    <t>乌尔比安</t>
+  </si>
+  <si>
+    <t>HUN-X</t>
+  </si>
+  <si>
+    <t>2019.05.06</t>
+  </si>
+  <si>
+    <t>历阵锐枪芬</t>
+  </si>
+  <si>
+    <t>深巡</t>
+  </si>
+  <si>
+    <t>蓝毒</t>
+  </si>
+  <si>
+    <t>苦艾</t>
+  </si>
+  <si>
+    <t>PHY-X</t>
+  </si>
+  <si>
+    <t>海霓</t>
+  </si>
+  <si>
+    <t>PhonoR-0</t>
+  </si>
+  <si>
+    <t>妮芙</t>
+  </si>
+  <si>
+    <t>渡桥</t>
+  </si>
+  <si>
+    <t>卡达</t>
+  </si>
+  <si>
+    <t>深海色</t>
+  </si>
+  <si>
+    <t>RPR-X</t>
+  </si>
+  <si>
+    <t>忍冬</t>
+  </si>
+  <si>
+    <t>佩佩</t>
+  </si>
+  <si>
+    <t>娜仁图亚</t>
+  </si>
+  <si>
+    <t>荒芜拉普兰德</t>
+  </si>
+  <si>
+    <t>玛露西尔</t>
+  </si>
+  <si>
+    <t>WAH-X</t>
+  </si>
+  <si>
+    <t>弑君者</t>
+  </si>
+  <si>
+    <t>引星棘刺</t>
+  </si>
+  <si>
+    <t>SOL-X</t>
+  </si>
+  <si>
+    <t>BAR-X</t>
+  </si>
+  <si>
+    <t>RIT-X</t>
+  </si>
+  <si>
+    <t>WDM-X</t>
+  </si>
+  <si>
+    <t>CRU-X</t>
+  </si>
+  <si>
+    <t>AFT-X</t>
+  </si>
+  <si>
+    <t>维娜·维多利亚</t>
+  </si>
+  <si>
+    <t>AFT-Δ</t>
+  </si>
+  <si>
+    <t>ISW-A</t>
+  </si>
+  <si>
+    <t>HAM-X</t>
+  </si>
+  <si>
+    <t>RA-A</t>
+  </si>
+  <si>
+    <t>余</t>
+  </si>
+  <si>
+    <t>BLA-D</t>
+  </si>
+  <si>
+    <t>烛煌</t>
+  </si>
+  <si>
+    <t>PUS-Y</t>
+  </si>
+  <si>
+    <t>2025.05.02</t>
+  </si>
+  <si>
+    <t>BEA-Y</t>
+  </si>
+  <si>
+    <t>AGE-Y</t>
+  </si>
+  <si>
+    <t>重岳</t>
+  </si>
+  <si>
+    <t>LIB-X</t>
+  </si>
+  <si>
+    <t>隐德来希</t>
+  </si>
+  <si>
+    <t>信仰搅拌机</t>
+  </si>
+  <si>
     <t>鸿雪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HOK-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMB-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>晓歌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿米娅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skin3</t>
-  </si>
-  <si>
-    <t>阿消</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>崖心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猎蜂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ARC-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛恩纳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRO-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRO-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>野鬃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四五星三技能填0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不填则随机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模组等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗小黑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泡泡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暗索</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒芒克洛丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>九色鹿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>食铁兽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>见行者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>海沫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白铁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOL-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伺夜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>斥罪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缄默德克萨斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夜魔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>贾维</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铅踝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>极光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUM-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>耶拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>焰影苇草</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石英</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重岳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCR-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火哨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>临光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谜图</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仇白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>铎铃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉维尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>截云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>因陀罗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断罪者</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麒麟X夜刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PUS-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火龙S黑角</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊内丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLX-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRP-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星极</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>缪尔赛思</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>霍尔海雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>淬羽赫默</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Castle-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>泰拉大陆调查团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正义骑士号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lancet-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>U-Official</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BOM-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHY-Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UMD-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>elite1</t>
-  </si>
-  <si>
-    <t>玫拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普罗旺斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特米米</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>真理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>古米</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坚雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗比菈塔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Friston-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣约送葬人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CRA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蕾缪安</t>
+  </si>
+  <si>
+    <t>DEA-Y</t>
+  </si>
+  <si>
+    <t>死芒</t>
+  </si>
+  <si>
+    <t>Mon3tr</t>
+  </si>
+  <si>
+    <t>新约能天使</t>
   </si>
   <si>
     <t>GEE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BEA-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提丰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SIE-X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寒檀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>空构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杰西卡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>THRM-EX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琳琅诗怀雅</t>
-  </si>
-  <si>
-    <t>MER-X</t>
-  </si>
-  <si>
-    <t>CEN-X</t>
-  </si>
-  <si>
-    <t>REA-X</t>
-  </si>
-  <si>
-    <t>纯烬艾雅法拉</t>
-  </si>
-  <si>
-    <t>BEA-X</t>
-  </si>
-  <si>
-    <t>青枳</t>
-  </si>
-  <si>
-    <t>涤火杰西卡</t>
-  </si>
-  <si>
-    <t>冰酿</t>
-  </si>
-  <si>
-    <t>杏仁</t>
-  </si>
-  <si>
-    <t>BLS-X</t>
-  </si>
-  <si>
-    <t>赫德雷</t>
-  </si>
-  <si>
-    <t>FOR-X</t>
-  </si>
-  <si>
-    <t>ARC-X</t>
-  </si>
-  <si>
-    <t>刺玫</t>
-  </si>
-  <si>
-    <t>薇薇安娜</t>
-  </si>
-  <si>
-    <t>止颂</t>
-  </si>
-  <si>
-    <t>UNY-X</t>
-  </si>
-  <si>
-    <t>塑心</t>
-  </si>
-  <si>
-    <t>锏</t>
-  </si>
-  <si>
-    <t>FUN-X</t>
-  </si>
-  <si>
-    <t>INC-X</t>
-  </si>
-  <si>
-    <t>DEC-Y</t>
-  </si>
-  <si>
-    <t>赤冬</t>
-  </si>
-  <si>
-    <t>烈夏</t>
-  </si>
-  <si>
-    <t>摩根</t>
-  </si>
-  <si>
-    <t>凛视</t>
-  </si>
-  <si>
-    <t>跃跃</t>
-  </si>
-  <si>
-    <t>杜宾</t>
-  </si>
-  <si>
-    <t>霜叶</t>
-  </si>
-  <si>
-    <t>莱伊</t>
-  </si>
-  <si>
-    <t>艾丝黛尔</t>
-  </si>
-  <si>
-    <t>FGT-Y</t>
-  </si>
-  <si>
-    <t>FGT-X</t>
-  </si>
-  <si>
-    <t>左乐</t>
-  </si>
-  <si>
-    <t>黍</t>
-  </si>
-  <si>
-    <t>万顷</t>
-  </si>
-  <si>
-    <t>小满</t>
-  </si>
-  <si>
-    <t>SBL-X</t>
-  </si>
-  <si>
-    <t>GUA-X</t>
-  </si>
-  <si>
-    <t>红隼</t>
-  </si>
-  <si>
-    <t>夜烟</t>
-  </si>
-  <si>
-    <t>SPT-X</t>
-  </si>
-  <si>
-    <t>艾拉</t>
-  </si>
-  <si>
-    <t>TRP-Δ</t>
-  </si>
-  <si>
-    <t>导火索</t>
-  </si>
-  <si>
-    <t>医生</t>
-  </si>
-  <si>
-    <t>双月</t>
-  </si>
-  <si>
-    <t>芳汀</t>
-  </si>
-  <si>
-    <t>AMB-X</t>
-  </si>
-  <si>
-    <t>杰克</t>
-  </si>
-  <si>
-    <t>酸糖</t>
-  </si>
-  <si>
-    <t>休谟斯</t>
-  </si>
-  <si>
-    <t>INS-Y</t>
-  </si>
-  <si>
-    <t>TAC-X</t>
-  </si>
-  <si>
-    <t>阿斯卡纶</t>
-  </si>
-  <si>
-    <t>LOR-X</t>
-  </si>
-  <si>
-    <t>维什戴尔</t>
-  </si>
-  <si>
-    <t>BOM-X</t>
-  </si>
-  <si>
-    <t>逻各斯</t>
-  </si>
-  <si>
-    <t>魔王</t>
-  </si>
-  <si>
-    <t>CCR-X</t>
-  </si>
-  <si>
-    <t>CCR-Δ</t>
-  </si>
-  <si>
-    <t>乌尔比安</t>
-  </si>
-  <si>
-    <t>HUN-X</t>
-  </si>
-  <si>
-    <t>2019.05.06</t>
-  </si>
-  <si>
-    <t>历阵锐枪芬</t>
-  </si>
-  <si>
-    <t>深巡</t>
-  </si>
-  <si>
-    <t>蓝毒</t>
-  </si>
-  <si>
-    <t>苦艾</t>
-  </si>
-  <si>
-    <t>PHY-X</t>
-  </si>
-  <si>
-    <t>海霓</t>
-  </si>
-  <si>
-    <t>PhonoR-0</t>
-  </si>
-  <si>
-    <t>妮芙</t>
-  </si>
-  <si>
-    <t>渡桥</t>
-  </si>
-  <si>
-    <t>卡达</t>
-  </si>
-  <si>
-    <t>深海色</t>
-  </si>
-  <si>
-    <t>RPR-X</t>
-  </si>
-  <si>
-    <t>忍冬</t>
-  </si>
-  <si>
-    <t>佩佩</t>
-  </si>
-  <si>
-    <t>娜仁图亚</t>
-  </si>
-  <si>
-    <t>荒芜拉普兰德</t>
-  </si>
-  <si>
-    <t>玛露西尔</t>
-  </si>
-  <si>
-    <t>WAH-X</t>
-  </si>
-  <si>
-    <t>弑君者</t>
-  </si>
-  <si>
-    <t>引星棘刺</t>
-  </si>
-  <si>
-    <t>SOL-X</t>
-  </si>
-  <si>
-    <t>BAR-X</t>
-  </si>
-  <si>
-    <t>RIT-X</t>
-  </si>
-  <si>
-    <t>WDM-X</t>
-  </si>
-  <si>
-    <t>CRU-X</t>
-  </si>
-  <si>
-    <t>AFT-X</t>
-  </si>
-  <si>
-    <t>维娜·维多利亚</t>
-  </si>
-  <si>
-    <t>AFT-Δ</t>
-  </si>
-  <si>
-    <t>ISW-A</t>
-  </si>
-  <si>
-    <t>HAM-X</t>
-  </si>
-  <si>
-    <t>RA-A</t>
-  </si>
-  <si>
-    <t>余</t>
-  </si>
-  <si>
-    <t>BLA-D</t>
-  </si>
-  <si>
-    <t>烛煌</t>
-  </si>
-  <si>
-    <t>PUS-Y</t>
-  </si>
-  <si>
-    <t>2025.02.13</t>
+  </si>
+  <si>
+    <t>ALC-X</t>
+  </si>
+  <si>
+    <t>CONFESS-47</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1912,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1883,7 +1920,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1899,7 +1936,7 @@
         <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1997,7 +2034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L268"/>
+  <dimension ref="A1:L278"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="19.15234375" customWidth="1"/>
@@ -2016,7 +2053,7 @@
       <c r="D1" s="11"/>
       <c r="E1" s="12"/>
       <c r="F1" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
@@ -2024,13 +2061,13 @@
         <v>55</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>211</v>
-      </c>
       <c r="L1" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2138,7 +2175,7 @@
         <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2187,7 +2224,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -2211,10 +2248,10 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -2249,10 +2286,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K7">
         <v>3</v>
@@ -2263,13 +2300,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>39</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -2287,27 +2324,27 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>372</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -2325,10 +2362,10 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J9" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2339,7 +2376,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -2363,10 +2400,10 @@
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J10" t="s">
-        <v>224</v>
+        <v>348</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -2377,13 +2414,13 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -2401,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J11" t="s">
         <v>223</v>
@@ -2410,18 +2447,18 @@
         <v>1</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2440,11 +2477,20 @@
       </c>
       <c r="I12" t="s">
         <v>57</v>
+      </c>
+      <c r="J12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -2471,24 +2517,24 @@
         <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>135</v>
+        <v>397</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="B14">
         <v>6</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2506,10 +2552,10 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J14" t="s">
-        <v>298</v>
+        <v>135</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -2520,7 +2566,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -2544,10 +2590,10 @@
         <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J15" t="s">
-        <v>136</v>
+        <v>296</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2558,13 +2604,13 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2585,7 +2631,7 @@
         <v>58</v>
       </c>
       <c r="J16" t="s">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2596,13 +2642,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>398</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2620,28 +2666,28 @@
         <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J17" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
         <v>1</v>
       </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
       <c r="D18">
         <v>2</v>
       </c>
@@ -2661,24 +2707,24 @@
         <v>57</v>
       </c>
       <c r="J18" t="s">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2699,18 +2745,18 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -2737,10 +2783,10 @@
         <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="K20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>161</v>
@@ -2748,13 +2794,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2772,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J21" t="s">
         <v>136</v>
@@ -2786,13 +2832,13 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2810,18 +2856,27 @@
         <v>10</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J22" t="s">
+        <v>350</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>203</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2839,27 +2894,27 @@
         <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J23" t="s">
-        <v>137</v>
+        <v>399</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>4</v>
       </c>
       <c r="B24">
         <v>6</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2877,13 +2932,13 @@
         <v>10</v>
       </c>
       <c r="I24" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J24" t="s">
-        <v>391</v>
+        <v>137</v>
       </c>
       <c r="K24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>161</v>
@@ -2891,14 +2946,14 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25">
         <v>5</v>
       </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
       <c r="D25">
         <v>2</v>
       </c>
@@ -2915,13 +2970,13 @@
         <v>10</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J25" t="s">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>161</v>
@@ -2929,7 +2984,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2953,21 +3008,21 @@
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J26" t="s">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="K26">
         <v>1</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -2994,10 +3049,10 @@
         <v>58</v>
       </c>
       <c r="J27" t="s">
-        <v>387</v>
+        <v>326</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>161</v>
@@ -3005,13 +3060,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>284</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -3032,18 +3087,18 @@
         <v>57</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>297</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29">
         <v>6</v>
@@ -3070,24 +3125,24 @@
         <v>58</v>
       </c>
       <c r="J29" t="s">
-        <v>159</v>
+        <v>385</v>
       </c>
       <c r="K29">
         <v>3</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>311</v>
+        <v>7</v>
       </c>
       <c r="B30">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -3105,10 +3160,10 @@
         <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J30" t="s">
-        <v>389</v>
+        <v>138</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -3119,13 +3174,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>388</v>
+        <v>7</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -3143,27 +3198,27 @@
         <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J31" t="s">
-        <v>387</v>
+        <v>159</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -3184,24 +3239,24 @@
         <v>165</v>
       </c>
       <c r="J32" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -3222,7 +3277,7 @@
         <v>57</v>
       </c>
       <c r="J33" t="s">
-        <v>138</v>
+        <v>387</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -3233,13 +3288,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="B34">
         <v>6</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -3257,21 +3312,21 @@
         <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="J34" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>312</v>
+        <v>8</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -3309,13 +3364,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>241</v>
+        <v>400</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -3333,27 +3388,27 @@
         <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="K36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>330</v>
+        <v>9</v>
       </c>
       <c r="B37">
         <v>6</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -3371,21 +3426,21 @@
         <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="J37" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -3409,65 +3464,65 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J38" t="s">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="K38">
         <v>3</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>90</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>57</v>
+      </c>
+      <c r="J39" t="s">
+        <v>332</v>
+      </c>
+      <c r="K39">
         <v>3</v>
       </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39">
-        <v>90</v>
-      </c>
-      <c r="F39">
-        <v>10</v>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-      <c r="H39">
-        <v>10</v>
-      </c>
-      <c r="I39" t="s">
-        <v>57</v>
-      </c>
-      <c r="J39" t="s">
-        <v>338</v>
-      </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
       <c r="L39" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -3485,27 +3540,27 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -3523,27 +3578,27 @@
         <v>10</v>
       </c>
       <c r="I41" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="K41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3561,27 +3616,27 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>206</v>
+        <v>306</v>
       </c>
       <c r="K42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3599,21 +3654,21 @@
         <v>10</v>
       </c>
       <c r="I43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J43" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="K43">
         <v>2</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -3637,21 +3692,21 @@
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="J44" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="K44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="B45">
         <v>6</v>
@@ -3678,10 +3733,10 @@
         <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>392</v>
+        <v>139</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>163</v>
@@ -3689,13 +3744,13 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -3713,21 +3768,21 @@
         <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J46" t="s">
-        <v>335</v>
+        <v>140</v>
       </c>
       <c r="K46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -3754,24 +3809,24 @@
         <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>141</v>
+        <v>390</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -3792,53 +3847,62 @@
         <v>57</v>
       </c>
       <c r="J48" t="s">
-        <v>205</v>
+        <v>333</v>
       </c>
       <c r="K48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>90</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>57</v>
+      </c>
+      <c r="J49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K49">
         <v>1</v>
       </c>
-      <c r="D49">
-        <v>2</v>
-      </c>
-      <c r="E49">
-        <v>90</v>
-      </c>
-      <c r="F49">
-        <v>10</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="H49">
-        <v>10</v>
-      </c>
-      <c r="I49" t="s">
-        <v>165</v>
+      <c r="L49" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -3859,24 +3923,24 @@
         <v>57</v>
       </c>
       <c r="J50" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>401</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -3885,36 +3949,36 @@
         <v>90</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I51" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J51" t="s">
-        <v>143</v>
+        <v>336</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>391</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -3932,27 +3996,18 @@
         <v>10</v>
       </c>
       <c r="I52" t="s">
-        <v>57</v>
-      </c>
-      <c r="J52" t="s">
-        <v>309</v>
-      </c>
-      <c r="K52">
-        <v>3</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -3973,10 +4028,10 @@
         <v>58</v>
       </c>
       <c r="J53" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>161</v>
@@ -3984,51 +4039,51 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54">
+        <v>6</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>90</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+      <c r="H54">
+        <v>10</v>
+      </c>
+      <c r="I54" t="s">
+        <v>57</v>
+      </c>
+      <c r="J54" t="s">
+        <v>307</v>
+      </c>
+      <c r="K54">
         <v>3</v>
       </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54">
-        <v>90</v>
-      </c>
-      <c r="F54">
-        <v>10</v>
-      </c>
-      <c r="G54">
-        <v>10</v>
-      </c>
-      <c r="H54">
-        <v>10</v>
-      </c>
-      <c r="I54" t="s">
-        <v>57</v>
-      </c>
-      <c r="J54" t="s">
-        <v>203</v>
-      </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
       <c r="L54" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -4046,13 +4101,13 @@
         <v>10</v>
       </c>
       <c r="I55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J55" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>161</v>
@@ -4060,13 +4115,13 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -4087,10 +4142,10 @@
         <v>57</v>
       </c>
       <c r="J56" t="s">
-        <v>373</v>
+        <v>202</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>161</v>
@@ -4098,13 +4153,13 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -4128,7 +4183,7 @@
         <v>183</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>161</v>
@@ -4136,13 +4191,13 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>326</v>
+        <v>87</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -4163,48 +4218,48 @@
         <v>57</v>
       </c>
       <c r="J58" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>90</v>
+      </c>
+      <c r="F59">
+        <v>10</v>
+      </c>
+      <c r="G59">
+        <v>10</v>
+      </c>
+      <c r="H59">
+        <v>10</v>
+      </c>
+      <c r="I59" t="s">
+        <v>57</v>
+      </c>
+      <c r="J59" t="s">
+        <v>183</v>
+      </c>
+      <c r="K59">
         <v>3</v>
-      </c>
-      <c r="D59">
-        <v>2</v>
-      </c>
-      <c r="E59">
-        <v>90</v>
-      </c>
-      <c r="F59">
-        <v>10</v>
-      </c>
-      <c r="G59">
-        <v>10</v>
-      </c>
-      <c r="H59">
-        <v>10</v>
-      </c>
-      <c r="I59" t="s">
-        <v>165</v>
-      </c>
-      <c r="J59" t="s">
-        <v>272</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>161</v>
@@ -4212,13 +4267,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -4236,56 +4291,65 @@
         <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J60" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>90</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>10</v>
+      </c>
+      <c r="I61" t="s">
+        <v>57</v>
+      </c>
+      <c r="J61" t="s">
+        <v>358</v>
+      </c>
+      <c r="K61">
         <v>3</v>
       </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61">
-        <v>90</v>
-      </c>
-      <c r="F61">
-        <v>10</v>
-      </c>
-      <c r="G61">
-        <v>10</v>
-      </c>
-      <c r="H61">
-        <v>10</v>
-      </c>
-      <c r="I61" t="s">
-        <v>165</v>
+      <c r="L61" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>403</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -4294,19 +4358,19 @@
         <v>90</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I62" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="J62" t="s">
-        <v>184</v>
+        <v>404</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -4317,7 +4381,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>290</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>6</v>
@@ -4341,13 +4405,13 @@
         <v>10</v>
       </c>
       <c r="I63" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J63" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>161</v>
@@ -4355,13 +4419,13 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>353</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -4379,21 +4443,21 @@
         <v>10</v>
       </c>
       <c r="I64" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J64" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="B65">
         <v>6</v>
@@ -4417,27 +4481,18 @@
         <v>10</v>
       </c>
       <c r="I65" t="s">
-        <v>57</v>
-      </c>
-      <c r="J65" t="s">
-        <v>144</v>
-      </c>
-      <c r="K65">
-        <v>2</v>
-      </c>
-      <c r="L65" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -4455,13 +4510,13 @@
         <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="J66" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="K66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>161</v>
@@ -4469,13 +4524,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>288</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -4493,10 +4548,10 @@
         <v>10</v>
       </c>
       <c r="I67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J67" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="K67">
         <v>3</v>
@@ -4507,13 +4562,13 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -4531,13 +4586,13 @@
         <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J68" t="s">
-        <v>316</v>
+        <v>142</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>161</v>
@@ -4545,13 +4600,13 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>351</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4572,10 +4627,10 @@
         <v>57</v>
       </c>
       <c r="J69" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>161</v>
@@ -4583,13 +4638,13 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>377</v>
+        <v>88</v>
       </c>
       <c r="B70">
         <v>6</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -4607,13 +4662,13 @@
         <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J70" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>161</v>
@@ -4621,13 +4676,13 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>264</v>
+        <v>89</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4648,10 +4703,10 @@
         <v>57</v>
       </c>
       <c r="J71" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>161</v>
@@ -4659,7 +4714,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B72">
         <v>6</v>
@@ -4683,21 +4738,21 @@
         <v>10</v>
       </c>
       <c r="I72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J72" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="K72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -4721,10 +4776,10 @@
         <v>10</v>
       </c>
       <c r="I73" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="J73" t="s">
-        <v>357</v>
+        <v>314</v>
       </c>
       <c r="K73">
         <v>3</v>
@@ -4735,13 +4790,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>91</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4762,18 +4817,18 @@
         <v>57</v>
       </c>
       <c r="J74" t="s">
-        <v>260</v>
+        <v>145</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B75">
         <v>6</v>
@@ -4800,7 +4855,7 @@
         <v>165</v>
       </c>
       <c r="J75" t="s">
-        <v>358</v>
+        <v>314</v>
       </c>
       <c r="K75">
         <v>3</v>
@@ -4811,13 +4866,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>378</v>
+        <v>262</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4835,21 +4890,21 @@
         <v>10</v>
       </c>
       <c r="I76" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J76" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -4873,27 +4928,27 @@
         <v>10</v>
       </c>
       <c r="I77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J77" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="K77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>369</v>
+        <v>92</v>
       </c>
       <c r="B78">
         <v>6</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -4911,18 +4966,27 @@
         <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J78" t="s">
+        <v>355</v>
+      </c>
+      <c r="K78">
+        <v>3</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4943,24 +5007,24 @@
         <v>57</v>
       </c>
       <c r="J79" t="s">
-        <v>147</v>
+        <v>258</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>353</v>
       </c>
       <c r="B80">
         <v>6</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -4981,24 +5045,24 @@
         <v>57</v>
       </c>
       <c r="J80" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="K80">
         <v>3</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>376</v>
       </c>
       <c r="B81">
         <v>6</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -5019,18 +5083,18 @@
         <v>57</v>
       </c>
       <c r="J81" t="s">
-        <v>257</v>
+        <v>146</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -5057,24 +5121,24 @@
         <v>58</v>
       </c>
       <c r="J82" t="s">
-        <v>394</v>
+        <v>146</v>
       </c>
       <c r="K82">
         <v>3</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>367</v>
       </c>
       <c r="B83">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -5093,26 +5157,17 @@
       </c>
       <c r="I83" t="s">
         <v>57</v>
-      </c>
-      <c r="J83" t="s">
-        <v>148</v>
-      </c>
-      <c r="K83">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -5135,13 +5190,13 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -5162,24 +5217,24 @@
         <v>57</v>
       </c>
       <c r="J85" t="s">
-        <v>385</v>
+        <v>147</v>
       </c>
       <c r="K85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -5197,13 +5252,13 @@
         <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J86" t="s">
-        <v>220</v>
+        <v>388</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>163</v>
@@ -5211,7 +5266,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B87">
         <v>6</v>
@@ -5238,18 +5293,18 @@
         <v>57</v>
       </c>
       <c r="J87" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B88">
         <v>6</v>
@@ -5273,10 +5328,10 @@
         <v>10</v>
       </c>
       <c r="I88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J88" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K88">
         <v>3</v>
@@ -5287,13 +5342,13 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="B89">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -5314,24 +5369,24 @@
         <v>57</v>
       </c>
       <c r="J89" t="s">
-        <v>379</v>
+        <v>148</v>
       </c>
       <c r="K89">
         <v>1</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -5349,27 +5404,18 @@
         <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>57</v>
-      </c>
-      <c r="J90" t="s">
-        <v>221</v>
-      </c>
-      <c r="K90">
-        <v>3</v>
-      </c>
-      <c r="L90" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="B91">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -5387,10 +5433,10 @@
         <v>10</v>
       </c>
       <c r="I91" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J91" t="s">
-        <v>317</v>
+        <v>383</v>
       </c>
       <c r="K91">
         <v>3</v>
@@ -5401,7 +5447,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B92">
         <v>6</v>
@@ -5425,10 +5471,10 @@
         <v>10</v>
       </c>
       <c r="I92" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J92" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K92">
         <v>1</v>
@@ -5439,7 +5485,7 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B93">
         <v>6</v>
@@ -5466,18 +5512,18 @@
         <v>57</v>
       </c>
       <c r="J93" t="s">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -5501,27 +5547,27 @@
         <v>10</v>
       </c>
       <c r="I94" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J94" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="K94">
         <v>3</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="B95">
         <v>6</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -5542,24 +5588,24 @@
         <v>57</v>
       </c>
       <c r="J95" t="s">
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="K95">
         <v>1</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>265</v>
+        <v>406</v>
       </c>
       <c r="B96">
         <v>6</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -5579,25 +5625,16 @@
       <c r="I96" t="s">
         <v>165</v>
       </c>
-      <c r="J96" t="s">
-        <v>306</v>
-      </c>
-      <c r="K96">
-        <v>1</v>
-      </c>
-      <c r="L96" s="8" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5618,24 +5655,24 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="K97">
         <v>3</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5656,18 +5693,18 @@
         <v>58</v>
       </c>
       <c r="J98" t="s">
-        <v>151</v>
+        <v>315</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B99">
         <v>6</v>
@@ -5691,21 +5728,21 @@
         <v>10</v>
       </c>
       <c r="I99" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="J99" t="s">
-        <v>318</v>
+        <v>149</v>
       </c>
       <c r="K99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="B100">
         <v>6</v>
@@ -5729,13 +5766,13 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J100" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>162</v>
@@ -5743,7 +5780,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B101">
         <v>6</v>
@@ -5767,27 +5804,27 @@
         <v>10</v>
       </c>
       <c r="I101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J101" t="s">
-        <v>153</v>
+        <v>388</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>356</v>
+        <v>221</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5805,21 +5842,21 @@
         <v>10</v>
       </c>
       <c r="I102" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J102" t="s">
-        <v>383</v>
+        <v>285</v>
       </c>
       <c r="K102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="B103">
         <v>6</v>
@@ -5846,18 +5883,18 @@
         <v>57</v>
       </c>
       <c r="J103" t="s">
-        <v>384</v>
+        <v>304</v>
       </c>
       <c r="K103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="B104">
         <v>6</v>
@@ -5884,24 +5921,24 @@
         <v>58</v>
       </c>
       <c r="J104" t="s">
-        <v>383</v>
+        <v>152</v>
       </c>
       <c r="K104">
         <v>3</v>
       </c>
       <c r="L104" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B105">
         <v>6</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5922,10 +5959,10 @@
         <v>58</v>
       </c>
       <c r="J105" t="s">
-        <v>288</v>
+        <v>151</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>162</v>
@@ -5933,13 +5970,13 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5957,10 +5994,10 @@
         <v>10</v>
       </c>
       <c r="I106" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="J106" t="s">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="K106">
         <v>3</v>
@@ -5971,13 +6008,13 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>339</v>
+        <v>23</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5998,7 +6035,7 @@
         <v>57</v>
       </c>
       <c r="J107" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="K107">
         <v>3</v>
@@ -6009,7 +6046,7 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="B108">
         <v>6</v>
@@ -6036,18 +6073,18 @@
         <v>57</v>
       </c>
       <c r="J108" t="s">
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="K108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>354</v>
       </c>
       <c r="B109">
         <v>6</v>
@@ -6071,10 +6108,10 @@
         <v>10</v>
       </c>
       <c r="I109" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J109" t="s">
-        <v>195</v>
+        <v>381</v>
       </c>
       <c r="K109">
         <v>3</v>
@@ -6085,7 +6122,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="B110">
         <v>6</v>
@@ -6109,10 +6146,10 @@
         <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J110" t="s">
-        <v>154</v>
+        <v>382</v>
       </c>
       <c r="K110">
         <v>3</v>
@@ -6123,7 +6160,7 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B111">
         <v>6</v>
@@ -6147,27 +6184,27 @@
         <v>10</v>
       </c>
       <c r="I111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J111" t="s">
-        <v>236</v>
+        <v>381</v>
       </c>
       <c r="K111">
         <v>3</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="B112">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -6188,18 +6225,18 @@
         <v>58</v>
       </c>
       <c r="J112" t="s">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="K112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>35</v>
+        <v>337</v>
       </c>
       <c r="B113">
         <v>6</v>
@@ -6226,10 +6263,10 @@
         <v>57</v>
       </c>
       <c r="J113" t="s">
-        <v>155</v>
+        <v>338</v>
       </c>
       <c r="K113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>162</v>
@@ -6237,13 +6274,13 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -6261,27 +6298,27 @@
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J114" t="s">
-        <v>390</v>
+        <v>195</v>
       </c>
       <c r="K114">
         <v>3</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="B115">
         <v>6</v>
       </c>
       <c r="C115">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -6302,56 +6339,56 @@
         <v>57</v>
       </c>
       <c r="J115" t="s">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="B116">
         <v>6</v>
       </c>
       <c r="C116">
+        <v>6</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+      <c r="E116">
+        <v>90</v>
+      </c>
+      <c r="F116">
+        <v>10</v>
+      </c>
+      <c r="G116">
+        <v>10</v>
+      </c>
+      <c r="H116">
+        <v>10</v>
+      </c>
+      <c r="I116" t="s">
+        <v>58</v>
+      </c>
+      <c r="J116" t="s">
+        <v>194</v>
+      </c>
+      <c r="K116">
         <v>3</v>
       </c>
-      <c r="D116">
-        <v>2</v>
-      </c>
-      <c r="E116">
-        <v>90</v>
-      </c>
-      <c r="F116">
-        <v>10</v>
-      </c>
-      <c r="G116">
-        <v>10</v>
-      </c>
-      <c r="H116">
-        <v>10</v>
-      </c>
-      <c r="I116" t="s">
-        <v>57</v>
-      </c>
-      <c r="J116" t="s">
-        <v>297</v>
-      </c>
-      <c r="K116">
-        <v>1</v>
-      </c>
       <c r="L116" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="B117">
         <v>6</v>
@@ -6378,18 +6415,18 @@
         <v>165</v>
       </c>
       <c r="J117" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K117">
         <v>3</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>380</v>
+        <v>54</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -6413,27 +6450,27 @@
         <v>10</v>
       </c>
       <c r="I118" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J118" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="B119">
         <v>6</v>
       </c>
       <c r="C119">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -6451,21 +6488,21 @@
         <v>10</v>
       </c>
       <c r="I119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J119" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L119" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -6492,10 +6529,10 @@
         <v>57</v>
       </c>
       <c r="J120" t="s">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="K120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>162</v>
@@ -6503,7 +6540,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B121">
         <v>6</v>
@@ -6530,117 +6567,135 @@
         <v>58</v>
       </c>
       <c r="J121" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="K121">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>381</v>
+        <v>95</v>
       </c>
       <c r="B122">
         <v>6</v>
       </c>
       <c r="C122">
+        <v>4</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+      <c r="E122">
+        <v>90</v>
+      </c>
+      <c r="F122">
+        <v>10</v>
+      </c>
+      <c r="G122">
+        <v>10</v>
+      </c>
+      <c r="H122">
+        <v>10</v>
+      </c>
+      <c r="I122" t="s">
+        <v>57</v>
+      </c>
+      <c r="J122" t="s">
+        <v>295</v>
+      </c>
+      <c r="K122">
         <v>1</v>
       </c>
-      <c r="D122">
-        <v>2</v>
-      </c>
-      <c r="E122">
-        <v>90</v>
-      </c>
-      <c r="F122">
-        <v>10</v>
-      </c>
-      <c r="G122">
-        <v>10</v>
-      </c>
-      <c r="H122">
-        <v>10</v>
-      </c>
-      <c r="I122" t="s">
-        <v>165</v>
+      <c r="L122" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C123">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D123">
         <v>2</v>
       </c>
       <c r="E123">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F123">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G123">
         <v>10</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J123" t="s">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" s="8" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>370</v>
+        <v>253</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D124">
         <v>2</v>
       </c>
       <c r="E124">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F124">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G124">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I124" t="s">
         <v>165</v>
       </c>
+      <c r="J124" t="s">
+        <v>155</v>
+      </c>
+      <c r="K124">
+        <v>3</v>
+      </c>
+      <c r="L124" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>336</v>
+        <v>378</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C125">
         <v>6</v>
@@ -6649,36 +6704,45 @@
         <v>2</v>
       </c>
       <c r="E125">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F125">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G125">
         <v>10</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I125" t="s">
         <v>165</v>
       </c>
+      <c r="J125" t="s">
+        <v>155</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="B126">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C126">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D126">
         <v>2</v>
       </c>
       <c r="E126">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F126">
         <v>10</v>
@@ -6687,13 +6751,13 @@
         <v>10</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I126" t="s">
         <v>57</v>
       </c>
       <c r="J126" t="s">
-        <v>301</v>
+        <v>195</v>
       </c>
       <c r="K126">
         <v>1</v>
@@ -6704,39 +6768,48 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D127">
         <v>2</v>
       </c>
       <c r="E127">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F127">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G127">
         <v>10</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I127" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J127" t="s">
+        <v>388</v>
+      </c>
+      <c r="K127">
+        <v>3</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>362</v>
+        <v>37</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C128">
         <v>6</v>
@@ -6745,27 +6818,36 @@
         <v>2</v>
       </c>
       <c r="E128">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F128">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G128">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I128" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J128" t="s">
+        <v>254</v>
+      </c>
+      <c r="K128">
+        <v>3</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C129">
         <v>6</v>
@@ -6774,82 +6856,109 @@
         <v>2</v>
       </c>
       <c r="E129">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F129">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G129">
         <v>10</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I129" t="s">
         <v>58</v>
       </c>
+      <c r="J129" t="s">
+        <v>394</v>
+      </c>
+      <c r="K129">
+        <v>3</v>
+      </c>
+      <c r="L129" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>247</v>
+        <v>407</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C130">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D130">
         <v>2</v>
       </c>
       <c r="E130">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F130">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G130">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I130" t="s">
         <v>165</v>
       </c>
+      <c r="J130" t="s">
+        <v>408</v>
+      </c>
+      <c r="K130">
+        <v>3</v>
+      </c>
+      <c r="L130" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>302</v>
+        <v>379</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C131">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D131">
         <v>2</v>
       </c>
       <c r="E131">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F131">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G131">
         <v>10</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I131" t="s">
         <v>165</v>
       </c>
+      <c r="J131" t="s">
+        <v>409</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>332</v>
+        <v>96</v>
       </c>
       <c r="B132">
         <v>5</v>
@@ -6873,18 +6982,27 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J132" t="s">
+        <v>222</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>197</v>
+        <v>368</v>
       </c>
       <c r="B133">
         <v>5</v>
       </c>
       <c r="C133">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -6893,21 +7011,21 @@
         <v>80</v>
       </c>
       <c r="F133">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>207</v>
+        <v>334</v>
       </c>
       <c r="B134">
         <v>5</v>
@@ -6922,21 +7040,21 @@
         <v>80</v>
       </c>
       <c r="F134">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G134">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B135">
         <v>5</v>
@@ -6951,7 +7069,7 @@
         <v>80</v>
       </c>
       <c r="F135">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G135">
         <v>10</v>
@@ -6961,11 +7079,20 @@
       </c>
       <c r="I135" t="s">
         <v>57</v>
+      </c>
+      <c r="J135" t="s">
+        <v>299</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="B136">
         <v>5</v>
@@ -6980,7 +7107,7 @@
         <v>80</v>
       </c>
       <c r="F136">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G136">
         <v>10</v>
@@ -6989,12 +7116,12 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>360</v>
       </c>
       <c r="B137">
         <v>5</v>
@@ -7012,24 +7139,24 @@
         <v>7</v>
       </c>
       <c r="G137">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H137">
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="B138">
         <v>5</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -7047,12 +7174,12 @@
         <v>0</v>
       </c>
       <c r="I138" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="B139">
         <v>5</v>
@@ -7070,27 +7197,18 @@
         <v>10</v>
       </c>
       <c r="G139">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139" t="s">
-        <v>57</v>
-      </c>
-      <c r="J139" t="s">
-        <v>137</v>
-      </c>
-      <c r="K139">
-        <v>1</v>
-      </c>
-      <c r="L139" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B140">
         <v>5</v>
@@ -7114,12 +7232,12 @@
         <v>0</v>
       </c>
       <c r="I140" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B141">
         <v>5</v>
@@ -7148,7 +7266,7 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="B142">
         <v>5</v>
@@ -7163,7 +7281,7 @@
         <v>80</v>
       </c>
       <c r="F142">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G142">
         <v>10</v>
@@ -7172,12 +7290,12 @@
         <v>0</v>
       </c>
       <c r="I142" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B143">
         <v>5</v>
@@ -7206,7 +7324,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="B144">
         <v>5</v>
@@ -7230,12 +7348,12 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="B145">
         <v>5</v>
@@ -7250,7 +7368,7 @@
         <v>80</v>
       </c>
       <c r="F145">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G145">
         <v>10</v>
@@ -7264,13 +7382,13 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>320</v>
+        <v>192</v>
       </c>
       <c r="B146">
         <v>5</v>
       </c>
       <c r="C146">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -7288,18 +7406,18 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>321</v>
+        <v>227</v>
       </c>
       <c r="B147">
         <v>5</v>
       </c>
       <c r="C147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D147">
         <v>2</v>
@@ -7317,12 +7435,12 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B148">
         <v>5</v>
@@ -7337,21 +7455,30 @@
         <v>80</v>
       </c>
       <c r="F148">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G148">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148" t="s">
         <v>57</v>
+      </c>
+      <c r="J148" t="s">
+        <v>137</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="B149">
         <v>5</v>
@@ -7375,18 +7502,18 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B150">
         <v>5</v>
       </c>
       <c r="C150">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -7404,12 +7531,12 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -7433,12 +7560,12 @@
         <v>0</v>
       </c>
       <c r="I151" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>103</v>
+        <v>218</v>
       </c>
       <c r="B152">
         <v>5</v>
@@ -7456,27 +7583,18 @@
         <v>10</v>
       </c>
       <c r="G152">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152" t="s">
         <v>57</v>
-      </c>
-      <c r="J152" t="s">
-        <v>298</v>
-      </c>
-      <c r="K152">
-        <v>3</v>
-      </c>
-      <c r="L152" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="B153">
         <v>5</v>
@@ -7491,7 +7609,7 @@
         <v>80</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G153">
         <v>10</v>
@@ -7500,12 +7618,12 @@
         <v>0</v>
       </c>
       <c r="I153" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B154">
         <v>5</v>
@@ -7531,25 +7649,16 @@
       <c r="I154" t="s">
         <v>57</v>
       </c>
-      <c r="J154" t="s">
-        <v>136</v>
-      </c>
-      <c r="K154">
-        <v>1</v>
-      </c>
-      <c r="L154" s="8" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="B155">
         <v>5</v>
       </c>
       <c r="C155">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -7567,12 +7676,12 @@
         <v>0</v>
       </c>
       <c r="I155" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>244</v>
+        <v>319</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -7587,10 +7696,10 @@
         <v>80</v>
       </c>
       <c r="F156">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G156">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H156">
         <v>0</v>
@@ -7601,13 +7710,13 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="B157">
         <v>5</v>
       </c>
       <c r="C157">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D157">
         <v>2</v>
@@ -7625,12 +7734,12 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B158">
         <v>5</v>
@@ -7654,18 +7763,18 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>106</v>
+        <v>340</v>
       </c>
       <c r="B159">
         <v>5</v>
       </c>
       <c r="C159">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -7674,21 +7783,21 @@
         <v>80</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G159">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7703,10 +7812,10 @@
         <v>80</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G160">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -7717,13 +7826,13 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="B161">
         <v>5</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D161">
         <v>2</v>
@@ -7735,24 +7844,33 @@
         <v>10</v>
       </c>
       <c r="G161">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J161" t="s">
+        <v>296</v>
+      </c>
+      <c r="K161">
+        <v>3</v>
+      </c>
+      <c r="L161" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>363</v>
+        <v>104</v>
       </c>
       <c r="B162">
         <v>5</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D162">
         <v>2</v>
@@ -7761,21 +7879,21 @@
         <v>80</v>
       </c>
       <c r="F162">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G162">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="B163">
         <v>5</v>
@@ -7790,21 +7908,30 @@
         <v>80</v>
       </c>
       <c r="F163">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G163">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163" t="s">
         <v>57</v>
+      </c>
+      <c r="J163" t="s">
+        <v>136</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>107</v>
+        <v>282</v>
       </c>
       <c r="B164">
         <v>5</v>
@@ -7819,7 +7946,7 @@
         <v>80</v>
       </c>
       <c r="F164">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -7829,20 +7956,11 @@
       </c>
       <c r="I164" t="s">
         <v>57</v>
-      </c>
-      <c r="J164" t="s">
-        <v>144</v>
-      </c>
-      <c r="K164">
-        <v>3</v>
-      </c>
-      <c r="L164" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="B165">
         <v>5</v>
@@ -7857,27 +7975,27 @@
         <v>80</v>
       </c>
       <c r="F165">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G165">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="B166">
         <v>5</v>
       </c>
       <c r="C166">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -7900,7 +8018,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B167">
         <v>5</v>
@@ -7915,7 +8033,7 @@
         <v>80</v>
       </c>
       <c r="F167">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G167">
         <v>10</v>
@@ -7925,20 +8043,11 @@
       </c>
       <c r="I167" t="s">
         <v>57</v>
-      </c>
-      <c r="J167" t="s">
-        <v>184</v>
-      </c>
-      <c r="K167">
-        <v>3</v>
-      </c>
-      <c r="L167" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>251</v>
+        <v>106</v>
       </c>
       <c r="B168">
         <v>5</v>
@@ -7953,21 +8062,21 @@
         <v>80</v>
       </c>
       <c r="F168">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G168">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>364</v>
+        <v>243</v>
       </c>
       <c r="B169">
         <v>5</v>
@@ -7982,7 +8091,7 @@
         <v>80</v>
       </c>
       <c r="F169">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G169">
         <v>7</v>
@@ -7991,18 +8100,18 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="B170">
         <v>5</v>
       </c>
       <c r="C170">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D170">
         <v>2</v>
@@ -8011,27 +8120,27 @@
         <v>80</v>
       </c>
       <c r="F170">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G170">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
       <c r="I170" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>277</v>
+        <v>361</v>
       </c>
       <c r="B171">
         <v>5</v>
       </c>
       <c r="C171">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D171">
         <v>2</v>
@@ -8043,18 +8152,18 @@
         <v>7</v>
       </c>
       <c r="G171">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
       <c r="I171" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="B172">
         <v>5</v>
@@ -8069,21 +8178,21 @@
         <v>80</v>
       </c>
       <c r="F172">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G172">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B173">
         <v>5</v>
@@ -8107,13 +8216,13 @@
         <v>0</v>
       </c>
       <c r="I173" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J173" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="K173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L173" s="8" t="s">
         <v>161</v>
@@ -8121,7 +8230,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B174">
         <v>5</v>
@@ -8150,7 +8259,7 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>112</v>
+        <v>302</v>
       </c>
       <c r="B175">
         <v>5</v>
@@ -8165,30 +8274,21 @@
         <v>80</v>
       </c>
       <c r="F175">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G175">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175" t="s">
-        <v>57</v>
-      </c>
-      <c r="J175" t="s">
-        <v>143</v>
-      </c>
-      <c r="K175">
-        <v>1</v>
-      </c>
-      <c r="L175" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:12">
       <c r="A176" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B176">
         <v>5</v>
@@ -8203,7 +8303,7 @@
         <v>80</v>
       </c>
       <c r="F176">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G176">
         <v>10</v>
@@ -8213,11 +8313,20 @@
       </c>
       <c r="I176" t="s">
         <v>57</v>
+      </c>
+      <c r="J176" t="s">
+        <v>184</v>
+      </c>
+      <c r="K176">
+        <v>3</v>
+      </c>
+      <c r="L176" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="B177">
         <v>5</v>
@@ -8232,27 +8341,27 @@
         <v>80</v>
       </c>
       <c r="F177">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G177">
         <v>10</v>
       </c>
       <c r="H177">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I177" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="178" spans="1:12">
       <c r="A178" t="s">
-        <v>113</v>
+        <v>362</v>
       </c>
       <c r="B178">
         <v>5</v>
       </c>
       <c r="C178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -8264,24 +8373,24 @@
         <v>7</v>
       </c>
       <c r="G178">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="B179">
         <v>5</v>
       </c>
       <c r="C179">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -8304,7 +8413,7 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>365</v>
+        <v>275</v>
       </c>
       <c r="B180">
         <v>5</v>
@@ -8322,7 +8431,7 @@
         <v>7</v>
       </c>
       <c r="G180">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H180">
         <v>0</v>
@@ -8333,7 +8442,7 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B181">
         <v>5</v>
@@ -8357,12 +8466,12 @@
         <v>0</v>
       </c>
       <c r="I181" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:12">
       <c r="A182" t="s">
-        <v>278</v>
+        <v>110</v>
       </c>
       <c r="B182">
         <v>5</v>
@@ -8377,7 +8486,7 @@
         <v>80</v>
       </c>
       <c r="F182">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G182">
         <v>10</v>
@@ -8386,12 +8495,21 @@
         <v>0</v>
       </c>
       <c r="I182" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J182" t="s">
+        <v>157</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="183" spans="1:12">
       <c r="A183" t="s">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="B183">
         <v>5</v>
@@ -8420,7 +8538,7 @@
     </row>
     <row r="184" spans="1:12">
       <c r="A184" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="B184">
         <v>5</v>
@@ -8435,21 +8553,30 @@
         <v>80</v>
       </c>
       <c r="F184">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G184">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184" t="s">
         <v>57</v>
+      </c>
+      <c r="J184" t="s">
+        <v>143</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+      <c r="L184" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="185" spans="1:12">
       <c r="A185" t="s">
-        <v>115</v>
+        <v>229</v>
       </c>
       <c r="B185">
         <v>5</v>
@@ -8475,25 +8602,16 @@
       <c r="I185" t="s">
         <v>57</v>
       </c>
-      <c r="J185" t="s">
-        <v>149</v>
-      </c>
-      <c r="K185">
-        <v>1</v>
-      </c>
-      <c r="L185" s="8" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>310</v>
+        <v>197</v>
       </c>
       <c r="B186">
         <v>5</v>
       </c>
       <c r="C186">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -8502,27 +8620,27 @@
         <v>80</v>
       </c>
       <c r="F186">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G186">
         <v>10</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I186" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="187" spans="1:12">
       <c r="A187" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B187">
         <v>5</v>
       </c>
       <c r="C187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -8531,7 +8649,7 @@
         <v>80</v>
       </c>
       <c r="F187">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G187">
         <v>10</v>
@@ -8540,27 +8658,18 @@
         <v>0</v>
       </c>
       <c r="I187" t="s">
-        <v>58</v>
-      </c>
-      <c r="J187" t="s">
-        <v>366</v>
-      </c>
-      <c r="K187">
-        <v>3</v>
-      </c>
-      <c r="L187" s="8" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="B188">
         <v>5</v>
       </c>
       <c r="C188">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D188">
         <v>2</v>
@@ -8569,21 +8678,21 @@
         <v>80</v>
       </c>
       <c r="F188">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G188">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H188">
         <v>0</v>
       </c>
       <c r="I188" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="189" spans="1:12">
       <c r="A189" t="s">
-        <v>118</v>
+        <v>363</v>
       </c>
       <c r="B189">
         <v>5</v>
@@ -8601,18 +8710,18 @@
         <v>7</v>
       </c>
       <c r="G189">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H189">
         <v>0</v>
       </c>
       <c r="I189" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B190">
         <v>5</v>
@@ -8627,7 +8736,7 @@
         <v>80</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G190">
         <v>10</v>
@@ -8636,12 +8745,12 @@
         <v>0</v>
       </c>
       <c r="I190" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" spans="1:12">
       <c r="A191" t="s">
-        <v>120</v>
+        <v>276</v>
       </c>
       <c r="B191">
         <v>5</v>
@@ -8670,13 +8779,13 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" t="s">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="B192">
         <v>5</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -8688,24 +8797,24 @@
         <v>7</v>
       </c>
       <c r="G192">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B193">
         <v>5</v>
       </c>
       <c r="C193">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D193">
         <v>2</v>
@@ -8728,7 +8837,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B194">
         <v>5</v>
@@ -8743,7 +8852,7 @@
         <v>80</v>
       </c>
       <c r="F194">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G194">
         <v>10</v>
@@ -8752,18 +8861,27 @@
         <v>0</v>
       </c>
       <c r="I194" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="J194" t="s">
+        <v>149</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="195" spans="1:12">
       <c r="A195" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="B195">
         <v>5</v>
       </c>
       <c r="C195">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -8786,7 +8904,7 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B196">
         <v>5</v>
@@ -8801,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="F196">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G196">
         <v>10</v>
@@ -8810,21 +8928,21 @@
         <v>0</v>
       </c>
       <c r="I196" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J196" t="s">
-        <v>153</v>
+        <v>364</v>
       </c>
       <c r="K196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="197" spans="1:12">
       <c r="A197" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B197">
         <v>5</v>
@@ -8842,18 +8960,18 @@
         <v>10</v>
       </c>
       <c r="G197">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H197">
         <v>0</v>
       </c>
       <c r="I197" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B198">
         <v>5</v>
@@ -8877,21 +8995,12 @@
         <v>0</v>
       </c>
       <c r="I198" t="s">
-        <v>57</v>
-      </c>
-      <c r="J198" t="s">
-        <v>153</v>
-      </c>
-      <c r="K198">
-        <v>1</v>
-      </c>
-      <c r="L198" s="8" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="B199">
         <v>5</v>
@@ -8906,7 +9015,7 @@
         <v>80</v>
       </c>
       <c r="F199">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G199">
         <v>10</v>
@@ -8920,7 +9029,7 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" t="s">
-        <v>333</v>
+        <v>120</v>
       </c>
       <c r="B200">
         <v>5</v>
@@ -8944,18 +9053,18 @@
         <v>0</v>
       </c>
       <c r="I200" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="201" spans="1:12">
       <c r="A201" t="s">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="B201">
         <v>5</v>
       </c>
       <c r="C201">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D201">
         <v>2</v>
@@ -8967,24 +9076,24 @@
         <v>7</v>
       </c>
       <c r="G201">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H201">
         <v>0</v>
       </c>
       <c r="I201" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:12">
       <c r="A202" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="B202">
         <v>5</v>
       </c>
       <c r="C202">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D202">
         <v>2</v>
@@ -9002,12 +9111,12 @@
         <v>0</v>
       </c>
       <c r="I202" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" spans="1:12">
       <c r="A203" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B203">
         <v>5</v>
@@ -9031,21 +9140,12 @@
         <v>0</v>
       </c>
       <c r="I203" t="s">
-        <v>57</v>
-      </c>
-      <c r="J203" t="s">
-        <v>154</v>
-      </c>
-      <c r="K203">
-        <v>1</v>
-      </c>
-      <c r="L203" s="8" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>127</v>
+        <v>320</v>
       </c>
       <c r="B204">
         <v>5</v>
@@ -9060,7 +9160,7 @@
         <v>80</v>
       </c>
       <c r="F204">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G204">
         <v>10</v>
@@ -9069,21 +9169,12 @@
         <v>0</v>
       </c>
       <c r="I204" t="s">
-        <v>57</v>
-      </c>
-      <c r="J204" t="s">
-        <v>158</v>
-      </c>
-      <c r="K204">
-        <v>1</v>
-      </c>
-      <c r="L204" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:12">
       <c r="A205" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B205">
         <v>5</v>
@@ -9098,7 +9189,7 @@
         <v>80</v>
       </c>
       <c r="F205">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G205">
         <v>10</v>
@@ -9110,7 +9201,7 @@
         <v>57</v>
       </c>
       <c r="J205" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K205">
         <v>1</v>
@@ -9121,7 +9212,7 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="B206">
         <v>5</v>
@@ -9136,7 +9227,7 @@
         <v>80</v>
       </c>
       <c r="F206">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G206">
         <v>10</v>
@@ -9150,7 +9241,7 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B207">
         <v>5</v>
@@ -9165,10 +9256,10 @@
         <v>80</v>
       </c>
       <c r="F207">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G207">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -9177,24 +9268,24 @@
         <v>57</v>
       </c>
       <c r="J207" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K207">
         <v>1</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>293</v>
+        <v>187</v>
       </c>
       <c r="B208">
         <v>5</v>
       </c>
       <c r="C208">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D208">
         <v>2</v>
@@ -9212,12 +9303,12 @@
         <v>0</v>
       </c>
       <c r="I208" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>130</v>
+        <v>331</v>
       </c>
       <c r="B209">
         <v>5</v>
@@ -9232,7 +9323,7 @@
         <v>80</v>
       </c>
       <c r="F209">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G209">
         <v>10</v>
@@ -9241,12 +9332,12 @@
         <v>0</v>
       </c>
       <c r="I209" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="B210">
         <v>5</v>
@@ -9261,30 +9352,21 @@
         <v>80</v>
       </c>
       <c r="F210">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G210">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H210">
         <v>0</v>
       </c>
       <c r="I210" t="s">
-        <v>58</v>
-      </c>
-      <c r="J210" t="s">
-        <v>345</v>
-      </c>
-      <c r="K210">
-        <v>1</v>
-      </c>
-      <c r="L210" s="8" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>217</v>
+        <v>125</v>
       </c>
       <c r="B211">
         <v>5</v>
@@ -9308,12 +9390,12 @@
         <v>0</v>
       </c>
       <c r="I211" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>343</v>
+        <v>126</v>
       </c>
       <c r="B212">
         <v>5</v>
@@ -9328,7 +9410,7 @@
         <v>80</v>
       </c>
       <c r="F212">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G212">
         <v>10</v>
@@ -9338,17 +9420,26 @@
       </c>
       <c r="I212" t="s">
         <v>57</v>
+      </c>
+      <c r="J212" t="s">
+        <v>154</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="213" spans="1:12">
       <c r="A213" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B213">
         <v>5</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D213">
         <v>2</v>
@@ -9357,7 +9448,7 @@
         <v>80</v>
       </c>
       <c r="F213">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G213">
         <v>10</v>
@@ -9366,12 +9457,21 @@
         <v>0</v>
       </c>
       <c r="I213" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J213" t="s">
+        <v>158</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>305</v>
+        <v>128</v>
       </c>
       <c r="B214">
         <v>5</v>
@@ -9386,7 +9486,7 @@
         <v>80</v>
       </c>
       <c r="F214">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G214">
         <v>10</v>
@@ -9395,12 +9495,21 @@
         <v>0</v>
       </c>
       <c r="I214" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J214" t="s">
+        <v>155</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="B215">
         <v>5</v>
@@ -9415,7 +9524,7 @@
         <v>80</v>
       </c>
       <c r="F215">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G215">
         <v>10</v>
@@ -9424,15 +9533,15 @@
         <v>0</v>
       </c>
       <c r="I215" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="B216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C216">
         <v>6</v>
@@ -9441,36 +9550,45 @@
         <v>2</v>
       </c>
       <c r="E216">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F216">
         <v>10</v>
       </c>
       <c r="G216">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H216">
         <v>0</v>
       </c>
       <c r="I216" t="s">
         <v>57</v>
+      </c>
+      <c r="J216" t="s">
+        <v>158</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>188</v>
+        <v>291</v>
       </c>
       <c r="B217">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C217">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D217">
         <v>2</v>
       </c>
       <c r="E217">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F217">
         <v>7</v>
@@ -9482,15 +9600,15 @@
         <v>0</v>
       </c>
       <c r="I217" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:12">
       <c r="A218" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="B218">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C218">
         <v>6</v>
@@ -9499,7 +9617,7 @@
         <v>2</v>
       </c>
       <c r="E218">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F218">
         <v>10</v>
@@ -9511,24 +9629,15 @@
         <v>0</v>
       </c>
       <c r="I218" t="s">
-        <v>58</v>
-      </c>
-      <c r="J218" t="s">
-        <v>301</v>
-      </c>
-      <c r="K218">
-        <v>3</v>
-      </c>
-      <c r="L218" s="8" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="219" spans="1:12">
       <c r="A219" t="s">
-        <v>327</v>
+        <v>131</v>
       </c>
       <c r="B219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C219">
         <v>6</v>
@@ -9537,27 +9646,36 @@
         <v>2</v>
       </c>
       <c r="E219">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F219">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G219">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J219" t="s">
+        <v>343</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="220" spans="1:12">
       <c r="A220" t="s">
-        <v>63</v>
+        <v>216</v>
       </c>
       <c r="B220">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C220">
         <v>6</v>
@@ -9566,10 +9684,10 @@
         <v>2</v>
       </c>
       <c r="E220">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F220">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G220">
         <v>10</v>
@@ -9578,24 +9696,15 @@
         <v>0</v>
       </c>
       <c r="I220" t="s">
-        <v>165</v>
-      </c>
-      <c r="J220" t="s">
-        <v>159</v>
-      </c>
-      <c r="K220">
-        <v>1</v>
-      </c>
-      <c r="L220" s="8" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
     </row>
     <row r="221" spans="1:12">
       <c r="A221" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B221">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C221">
         <v>6</v>
@@ -9604,65 +9713,56 @@
         <v>2</v>
       </c>
       <c r="E221">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F221">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G221">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H221">
         <v>0</v>
       </c>
       <c r="I221" t="s">
         <v>57</v>
-      </c>
-      <c r="J221" t="s">
-        <v>349</v>
-      </c>
-      <c r="K221">
-        <v>1</v>
-      </c>
-      <c r="L221" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="222" spans="1:12">
       <c r="A222" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="B222">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D222">
         <v>2</v>
       </c>
       <c r="E222">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F222">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G222">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H222">
         <v>0</v>
       </c>
       <c r="I222" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:12">
       <c r="A223" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="B223">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C223">
         <v>6</v>
@@ -9671,7 +9771,7 @@
         <v>2</v>
       </c>
       <c r="E223">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F223">
         <v>7</v>
@@ -9683,15 +9783,15 @@
         <v>0</v>
       </c>
       <c r="I223" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:12">
       <c r="A224" t="s">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="B224">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C224">
         <v>6</v>
@@ -9700,7 +9800,7 @@
         <v>2</v>
       </c>
       <c r="E224">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F224">
         <v>7</v>
@@ -9712,12 +9812,12 @@
         <v>0</v>
       </c>
       <c r="I224" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:12">
       <c r="A225" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B225">
         <v>4</v>
@@ -9735,18 +9835,18 @@
         <v>10</v>
       </c>
       <c r="G225">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H225">
         <v>0</v>
       </c>
       <c r="I225" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="226" spans="1:12">
       <c r="A226" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B226">
         <v>4</v>
@@ -9770,18 +9870,18 @@
         <v>0</v>
       </c>
       <c r="I226" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:12">
       <c r="A227" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="B227">
         <v>4</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D227">
         <v>2</v>
@@ -9793,18 +9893,27 @@
         <v>10</v>
       </c>
       <c r="G227">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227" t="s">
-        <v>275</v>
+        <v>58</v>
+      </c>
+      <c r="J227" t="s">
+        <v>299</v>
+      </c>
+      <c r="K227">
+        <v>3</v>
+      </c>
+      <c r="L227" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="228" spans="1:12">
       <c r="A228" t="s">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="B228">
         <v>4</v>
@@ -9819,21 +9928,21 @@
         <v>70</v>
       </c>
       <c r="F228">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G228">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:12">
       <c r="A229" t="s">
-        <v>240</v>
+        <v>63</v>
       </c>
       <c r="B229">
         <v>4</v>
@@ -9848,7 +9957,7 @@
         <v>70</v>
       </c>
       <c r="F229">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G229">
         <v>10</v>
@@ -9859,10 +9968,19 @@
       <c r="I229" t="s">
         <v>165</v>
       </c>
+      <c r="J229" t="s">
+        <v>159</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="L229" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="230" spans="1:12">
       <c r="A230" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B230">
         <v>4</v>
@@ -9877,27 +9995,36 @@
         <v>70</v>
       </c>
       <c r="F230">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G230">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230" t="s">
         <v>57</v>
+      </c>
+      <c r="J230" t="s">
+        <v>347</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="231" spans="1:12">
       <c r="A231" t="s">
-        <v>348</v>
+        <v>252</v>
       </c>
       <c r="B231">
         <v>4</v>
       </c>
       <c r="C231">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D231">
         <v>2</v>
@@ -9906,21 +10033,21 @@
         <v>70</v>
       </c>
       <c r="F231">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G231">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H231">
         <v>0</v>
       </c>
       <c r="I231" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="232" spans="1:12">
       <c r="A232" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B232">
         <v>4</v>
@@ -9935,7 +10062,7 @@
         <v>70</v>
       </c>
       <c r="F232">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G232">
         <v>10</v>
@@ -9944,12 +10071,12 @@
         <v>0</v>
       </c>
       <c r="I232" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="233" spans="1:12">
       <c r="A233" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="B233">
         <v>4</v>
@@ -9964,7 +10091,7 @@
         <v>70</v>
       </c>
       <c r="F233">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G233">
         <v>10</v>
@@ -9978,7 +10105,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>281</v>
+        <v>64</v>
       </c>
       <c r="B234">
         <v>4</v>
@@ -9993,10 +10120,10 @@
         <v>70</v>
       </c>
       <c r="F234">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G234">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -10007,7 +10134,7 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B235">
         <v>4</v>
@@ -10031,18 +10158,18 @@
         <v>0</v>
       </c>
       <c r="I235" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="236" spans="1:12">
       <c r="A236" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="B236">
         <v>4</v>
       </c>
       <c r="C236">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D236">
         <v>2</v>
@@ -10051,21 +10178,21 @@
         <v>70</v>
       </c>
       <c r="F236">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G236">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236" t="s">
-        <v>57</v>
+        <v>273</v>
       </c>
     </row>
     <row r="237" spans="1:12">
       <c r="A237" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B237">
         <v>4</v>
@@ -10080,30 +10207,21 @@
         <v>70</v>
       </c>
       <c r="F237">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G237">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H237">
         <v>0</v>
       </c>
       <c r="I237" t="s">
         <v>57</v>
-      </c>
-      <c r="J237" t="s">
-        <v>157</v>
-      </c>
-      <c r="K237">
-        <v>1</v>
-      </c>
-      <c r="L237" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="238" spans="1:12">
       <c r="A238" t="s">
-        <v>68</v>
+        <v>239</v>
       </c>
       <c r="B238">
         <v>4</v>
@@ -10127,21 +10245,12 @@
         <v>0</v>
       </c>
       <c r="I238" t="s">
-        <v>69</v>
-      </c>
-      <c r="J238" t="s">
-        <v>143</v>
-      </c>
-      <c r="K238">
-        <v>1</v>
-      </c>
-      <c r="L238" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:12">
       <c r="A239" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="B239">
         <v>4</v>
@@ -10170,7 +10279,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>346</v>
       </c>
       <c r="B240">
         <v>4</v>
@@ -10185,21 +10294,21 @@
         <v>70</v>
       </c>
       <c r="F240">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G240">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H240">
         <v>0</v>
       </c>
       <c r="I240" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:12">
       <c r="A241" t="s">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="B241">
         <v>4</v>
@@ -10217,18 +10326,18 @@
         <v>10</v>
       </c>
       <c r="G241">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H241">
         <v>0</v>
       </c>
       <c r="I241" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="242" spans="1:12">
       <c r="A242" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="B242">
         <v>4</v>
@@ -10243,7 +10352,7 @@
         <v>70</v>
       </c>
       <c r="F242">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G242">
         <v>10</v>
@@ -10257,7 +10366,7 @@
     </row>
     <row r="243" spans="1:12">
       <c r="A243" t="s">
-        <v>70</v>
+        <v>279</v>
       </c>
       <c r="B243">
         <v>4</v>
@@ -10272,7 +10381,7 @@
         <v>70</v>
       </c>
       <c r="F243">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G243">
         <v>10</v>
@@ -10281,12 +10390,12 @@
         <v>0</v>
       </c>
       <c r="I243" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:12">
       <c r="A244" t="s">
-        <v>347</v>
+        <v>212</v>
       </c>
       <c r="B244">
         <v>4</v>
@@ -10310,12 +10419,12 @@
         <v>0</v>
       </c>
       <c r="I244" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:12">
       <c r="A245" t="s">
-        <v>323</v>
+        <v>71</v>
       </c>
       <c r="B245">
         <v>4</v>
@@ -10330,7 +10439,7 @@
         <v>70</v>
       </c>
       <c r="F245">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G245">
         <v>10</v>
@@ -10339,12 +10448,12 @@
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="246" spans="1:12">
       <c r="A246" t="s">
-        <v>371</v>
+        <v>67</v>
       </c>
       <c r="B246">
         <v>4</v>
@@ -10370,10 +10479,19 @@
       <c r="I246" t="s">
         <v>57</v>
       </c>
+      <c r="J246" t="s">
+        <v>157</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246" s="8" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="247" spans="1:12">
       <c r="A247" t="s">
-        <v>337</v>
+        <v>68</v>
       </c>
       <c r="B247">
         <v>4</v>
@@ -10397,12 +10515,21 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>165</v>
+        <v>69</v>
+      </c>
+      <c r="J247" t="s">
+        <v>143</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="248" spans="1:12">
       <c r="A248" t="s">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="B248">
         <v>4</v>
@@ -10417,7 +10544,7 @@
         <v>70</v>
       </c>
       <c r="F248">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G248">
         <v>10</v>
@@ -10427,20 +10554,11 @@
       </c>
       <c r="I248" t="s">
         <v>57</v>
-      </c>
-      <c r="J248" t="s">
-        <v>190</v>
-      </c>
-      <c r="K248">
-        <v>1</v>
-      </c>
-      <c r="L248" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="249" spans="1:12">
       <c r="A249" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="B249">
         <v>4</v>
@@ -10469,7 +10587,7 @@
     </row>
     <row r="250" spans="1:12">
       <c r="A250" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="B250">
         <v>4</v>
@@ -10484,10 +10602,10 @@
         <v>70</v>
       </c>
       <c r="F250">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G250">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -10495,19 +10613,10 @@
       <c r="I250" t="s">
         <v>165</v>
       </c>
-      <c r="J250" t="s">
-        <v>160</v>
-      </c>
-      <c r="K250">
-        <v>1</v>
-      </c>
-      <c r="L250" s="8" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="251" spans="1:12">
       <c r="A251" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="B251">
         <v>4</v>
@@ -10536,7 +10645,7 @@
     </row>
     <row r="252" spans="1:12">
       <c r="A252" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B252">
         <v>4</v>
@@ -10562,19 +10671,10 @@
       <c r="I252" t="s">
         <v>57</v>
       </c>
-      <c r="J252" t="s">
-        <v>151</v>
-      </c>
-      <c r="K252">
-        <v>1</v>
-      </c>
-      <c r="L252" s="8" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>282</v>
+        <v>345</v>
       </c>
       <c r="B253">
         <v>4</v>
@@ -10603,7 +10703,7 @@
     </row>
     <row r="254" spans="1:12">
       <c r="A254" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="B254">
         <v>4</v>
@@ -10618,7 +10718,7 @@
         <v>70</v>
       </c>
       <c r="F254">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G254">
         <v>10</v>
@@ -10627,12 +10727,12 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="255" spans="1:12">
       <c r="A255" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B255">
         <v>4</v>
@@ -10650,7 +10750,7 @@
         <v>7</v>
       </c>
       <c r="G255">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -10661,7 +10761,7 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" t="s">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="B256">
         <v>4</v>
@@ -10676,21 +10776,21 @@
         <v>70</v>
       </c>
       <c r="F256">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G256">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H256">
         <v>0</v>
       </c>
       <c r="I256" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="257" spans="1:12">
       <c r="A257" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="B257">
         <v>4</v>
@@ -10705,7 +10805,7 @@
         <v>70</v>
       </c>
       <c r="F257">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G257">
         <v>10</v>
@@ -10714,12 +10814,21 @@
         <v>0</v>
       </c>
       <c r="I257" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="J257" t="s">
+        <v>190</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+      <c r="L257" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="258" spans="1:12">
       <c r="A258" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="B258">
         <v>4</v>
@@ -10737,27 +10846,18 @@
         <v>10</v>
       </c>
       <c r="G258">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H258">
         <v>0</v>
       </c>
       <c r="I258" t="s">
         <v>57</v>
-      </c>
-      <c r="J258" t="s">
-        <v>156</v>
-      </c>
-      <c r="K258">
-        <v>1</v>
-      </c>
-      <c r="L258" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="259" spans="1:12">
       <c r="A259" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B259">
         <v>4</v>
@@ -10772,7 +10872,7 @@
         <v>70</v>
       </c>
       <c r="F259">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G259">
         <v>10</v>
@@ -10781,13 +10881,13 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J259" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K259">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L259" s="8" t="s">
         <v>162</v>
@@ -10795,7 +10895,7 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" t="s">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="B260">
         <v>4</v>
@@ -10824,112 +10924,121 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="B261">
+        <v>4</v>
+      </c>
+      <c r="C261">
+        <v>6</v>
+      </c>
+      <c r="D261">
+        <v>2</v>
+      </c>
+      <c r="E261">
+        <v>70</v>
+      </c>
+      <c r="F261">
+        <v>10</v>
+      </c>
+      <c r="G261">
+        <v>10</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261" t="s">
+        <v>57</v>
+      </c>
+      <c r="J261" t="s">
+        <v>151</v>
+      </c>
+      <c r="K261">
         <v>1</v>
       </c>
-      <c r="C261">
-        <v>6</v>
-      </c>
-      <c r="D261">
-        <v>0</v>
-      </c>
-      <c r="E261">
-        <v>30</v>
-      </c>
-      <c r="F261">
-        <v>0</v>
-      </c>
-      <c r="G261">
-        <v>0</v>
-      </c>
-      <c r="H261">
-        <v>0</v>
-      </c>
-      <c r="I261" t="s">
-        <v>57</v>
+      <c r="L261" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B262">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C262">
         <v>6</v>
       </c>
       <c r="D262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E262">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F262">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G262">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H262">
         <v>0</v>
       </c>
       <c r="I262" t="s">
-        <v>275</v>
+        <v>57</v>
       </c>
     </row>
     <row r="263" spans="1:12">
       <c r="A263" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B263">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C263">
         <v>6</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E263">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H263">
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="264" spans="1:12">
       <c r="A264" t="s">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="B264">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C264">
         <v>6</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E264">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F264">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G264">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -10940,25 +11049,25 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B265">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C265">
         <v>6</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E265">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H265">
         <v>0</v>
@@ -10969,93 +11078,401 @@
     </row>
     <row r="266" spans="1:12">
       <c r="A266" t="s">
-        <v>368</v>
+        <v>213</v>
       </c>
       <c r="B266">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C266">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E266">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F266">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G266">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H266">
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>275</v>
+        <v>58</v>
       </c>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" t="s">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="B267">
+        <v>4</v>
+      </c>
+      <c r="C267">
+        <v>6</v>
+      </c>
+      <c r="D267">
+        <v>2</v>
+      </c>
+      <c r="E267">
+        <v>70</v>
+      </c>
+      <c r="F267">
+        <v>10</v>
+      </c>
+      <c r="G267">
+        <v>10</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267" t="s">
+        <v>57</v>
+      </c>
+      <c r="J267" t="s">
+        <v>156</v>
+      </c>
+      <c r="K267">
         <v>1</v>
       </c>
-      <c r="C267">
-        <v>6</v>
-      </c>
-      <c r="D267">
-        <v>0</v>
-      </c>
-      <c r="E267">
-        <v>30</v>
-      </c>
-      <c r="F267">
-        <v>0</v>
-      </c>
-      <c r="G267">
-        <v>0</v>
-      </c>
-      <c r="H267">
-        <v>0</v>
-      </c>
-      <c r="I267" t="s">
-        <v>275</v>
+      <c r="L267" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="268" spans="1:12">
       <c r="A268" t="s">
-        <v>295</v>
+        <v>75</v>
       </c>
       <c r="B268">
+        <v>4</v>
+      </c>
+      <c r="C268">
+        <v>6</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+      <c r="E268">
+        <v>70</v>
+      </c>
+      <c r="F268">
+        <v>10</v>
+      </c>
+      <c r="G268">
+        <v>10</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268" t="s">
+        <v>57</v>
+      </c>
+      <c r="J268" t="s">
+        <v>155</v>
+      </c>
+      <c r="K268">
+        <v>3</v>
+      </c>
+      <c r="L268" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12">
+      <c r="A269" t="s">
+        <v>76</v>
+      </c>
+      <c r="B269">
+        <v>4</v>
+      </c>
+      <c r="C269">
+        <v>6</v>
+      </c>
+      <c r="D269">
+        <v>2</v>
+      </c>
+      <c r="E269">
+        <v>70</v>
+      </c>
+      <c r="F269">
+        <v>7</v>
+      </c>
+      <c r="G269">
+        <v>10</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12">
+      <c r="A270" t="s">
+        <v>410</v>
+      </c>
+      <c r="B270">
         <v>1</v>
       </c>
-      <c r="C268">
-        <v>6</v>
-      </c>
-      <c r="D268">
-        <v>0</v>
-      </c>
-      <c r="E268">
+      <c r="C270">
+        <v>1</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
         <v>30</v>
       </c>
-      <c r="F268">
-        <v>0</v>
-      </c>
-      <c r="G268">
-        <v>0</v>
-      </c>
-      <c r="H268">
-        <v>0</v>
-      </c>
-      <c r="I268" t="s">
-        <v>275</v>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>0</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12">
+      <c r="A271" t="s">
+        <v>264</v>
+      </c>
+      <c r="B271">
+        <v>1</v>
+      </c>
+      <c r="C271">
+        <v>6</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>30</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12">
+      <c r="A272" t="s">
+        <v>283</v>
+      </c>
+      <c r="B272">
+        <v>1</v>
+      </c>
+      <c r="C272">
+        <v>6</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>30</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" t="s">
+        <v>265</v>
+      </c>
+      <c r="B273">
+        <v>1</v>
+      </c>
+      <c r="C273">
+        <v>6</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>30</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" t="s">
+        <v>266</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274">
+        <v>6</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>30</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" t="s">
+        <v>267</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275">
+        <v>6</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>30</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" t="s">
+        <v>366</v>
+      </c>
+      <c r="B276">
+        <v>1</v>
+      </c>
+      <c r="C276">
+        <v>6</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>30</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" t="s">
+        <v>268</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277">
+        <v>6</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>30</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" t="s">
+        <v>293</v>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278">
+        <v>6</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>30</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L260" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:L269" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -11067,20 +11484,20 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I269:I296" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I279:I306" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
       <formula1>"elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L302:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L312:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
       <formula1>"蓝色,绿色,灰色,红色,金色"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1048576" xr:uid="{067929F4-68AD-4FCF-9645-B8AA87BCECB2}">
       <formula1>0</formula1>
       <formula2>90</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L301" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L311" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
       <formula1>"blue,green,grey,red,yellow"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I268" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I278" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
       <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">

--- a/Source/arkD.xlsx
+++ b/Source/arkD.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37b141e1e60375e0/Arknights/ArknightsIDcard-Ebranch/ArknightsIDCard/Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{07D95BDE-5E8B-4E78-91B2-53470496501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B20ECC4-9D76-4ADB-A28D-E5C31030D5EE}"/>
+  <xr:revisionPtr revIDLastSave="768" documentId="13_ncr:1_{07D95BDE-5E8B-4E78-91B2-53470496501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D123ACA-78EC-4558-8645-C50D68A00BE1}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="14620" windowHeight="25220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="11596" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="其他信息" sheetId="2" r:id="rId1"/>
     <sheet name="练度表" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">练度表!$A$1:$L$308</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="454">
   <si>
     <t>陈</t>
   </si>
@@ -1407,9 +1407,6 @@
     <t>PUS-Y</t>
   </si>
   <si>
-    <t>2025.05.02</t>
-  </si>
-  <si>
     <t>BEA-Y</t>
   </si>
   <si>
@@ -1453,6 +1450,138 @@
   </si>
   <si>
     <t>CONFESS-47</t>
+  </si>
+  <si>
+    <t>2025.08.09</t>
+  </si>
+  <si>
+    <t>司霆惊蛰</t>
+  </si>
+  <si>
+    <t>PRO-X</t>
+  </si>
+  <si>
+    <t>斩业星熊</t>
+  </si>
+  <si>
+    <t>RPR-Y</t>
+  </si>
+  <si>
+    <t>FUN-Y</t>
+  </si>
+  <si>
+    <t>CCR-Y</t>
+  </si>
+  <si>
+    <t>SPC-X</t>
+  </si>
+  <si>
+    <t>PRI-X</t>
+  </si>
+  <si>
+    <t>SOC-X</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>SO-A</t>
+  </si>
+  <si>
+    <t>酒神</t>
+  </si>
+  <si>
+    <t>遥</t>
+  </si>
+  <si>
+    <t>BLS-Y</t>
+  </si>
+  <si>
+    <t>EXE-Y</t>
+  </si>
+  <si>
+    <t>贾维</t>
+  </si>
+  <si>
+    <t>齐尔查克</t>
+  </si>
+  <si>
+    <t>松桐</t>
+  </si>
+  <si>
+    <t>寻澜</t>
+  </si>
+  <si>
+    <t>芙兰卡</t>
+  </si>
+  <si>
+    <t>莱欧斯</t>
+  </si>
+  <si>
+    <t>聆音</t>
+  </si>
+  <si>
+    <t>龙舌兰</t>
+  </si>
+  <si>
+    <t>菲莱</t>
+  </si>
+  <si>
+    <t>森西</t>
+  </si>
+  <si>
+    <t>承曦格雷伊</t>
+  </si>
+  <si>
+    <t>吉星</t>
+  </si>
+  <si>
+    <t>慑砂</t>
+  </si>
+  <si>
+    <t>惊蛰</t>
+  </si>
+  <si>
+    <t>Miss.Christine</t>
+  </si>
+  <si>
+    <t>特克诺</t>
+  </si>
+  <si>
+    <t>瑰盐</t>
+  </si>
+  <si>
+    <t>录武官</t>
+  </si>
+  <si>
+    <t>莎草</t>
+  </si>
+  <si>
+    <t>衡沙</t>
+  </si>
+  <si>
+    <t>裁度</t>
+  </si>
+  <si>
+    <t>钼铅</t>
+  </si>
+  <si>
+    <t>锡人</t>
+  </si>
+  <si>
+    <t>清道夫</t>
+  </si>
+  <si>
+    <t>讯使</t>
+  </si>
+  <si>
+    <t>露托</t>
+  </si>
+  <si>
+    <t>红云</t>
+  </si>
+  <si>
+    <t>云迹</t>
   </si>
 </sst>
 </file>
@@ -1878,11 +2007,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6345695-2B66-457B-8BCC-599D10A5115F}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.4609375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.4609375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.84375" style="2"/>
+    <col min="1" max="1" width="20.46484375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.46484375" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.86328125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1920,7 +2049,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2034,15 +2163,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L278"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <dimension ref="A1:L318"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.15234375" customWidth="1"/>
-    <col min="9" max="9" width="10.3828125" customWidth="1"/>
-    <col min="12" max="12" width="8.84375" style="8"/>
+    <col min="1" max="1" width="19.1328125" customWidth="1"/>
+    <col min="9" max="9" width="10.3984375" customWidth="1"/>
+    <col min="12" max="12" width="8.86328125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="13" customFormat="1" ht="37.299999999999997" customHeight="1">
+    <row r="1" spans="1:12" s="13" customFormat="1" ht="37.35" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>49</v>
       </c>
@@ -2108,7 +2237,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="32.5" customHeight="1">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="32.549999999999997" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>166</v>
       </c>
@@ -2210,7 +2339,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="J5" t="s">
         <v>134</v>
@@ -2327,7 +2456,7 @@
         <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K8">
         <v>3</v>
@@ -2514,10 +2643,10 @@
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K13">
         <v>3</v>
@@ -2642,7 +2771,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2897,7 +3026,7 @@
         <v>58</v>
       </c>
       <c r="J23" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -2984,13 +3113,13 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>373</v>
       </c>
       <c r="B26">
         <v>6</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -3008,27 +3137,27 @@
         <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J26" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>246</v>
       </c>
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -3049,7 +3178,7 @@
         <v>58</v>
       </c>
       <c r="J27" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -3060,13 +3189,13 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>5</v>
       </c>
       <c r="B28">
         <v>6</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -3084,27 +3213,27 @@
         <v>10</v>
       </c>
       <c r="I28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J28" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>284</v>
       </c>
       <c r="B29">
         <v>6</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -3122,21 +3251,21 @@
         <v>10</v>
       </c>
       <c r="I29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J29" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30">
         <v>6</v>
@@ -3160,10 +3289,10 @@
         <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>385</v>
       </c>
       <c r="K30">
         <v>3</v>
@@ -3198,27 +3327,27 @@
         <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J31" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="K31">
         <v>3</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>386</v>
+        <v>7</v>
       </c>
       <c r="B32">
         <v>6</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -3236,27 +3365,27 @@
         <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J32" t="s">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="K32">
         <v>3</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>309</v>
+        <v>411</v>
       </c>
       <c r="B33">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -3274,21 +3403,21 @@
         <v>10</v>
       </c>
       <c r="I33" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J33" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="K33">
         <v>3</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -3315,24 +3444,24 @@
         <v>165</v>
       </c>
       <c r="J34" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -3353,7 +3482,7 @@
         <v>57</v>
       </c>
       <c r="J35" t="s">
-        <v>138</v>
+        <v>387</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -3364,13 +3493,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>400</v>
+        <v>357</v>
       </c>
       <c r="B36">
         <v>6</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -3388,13 +3517,13 @@
         <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J36" t="s">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>163</v>
@@ -3402,7 +3531,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37">
         <v>6</v>
@@ -3426,10 +3555,10 @@
         <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="J37" t="s">
-        <v>350</v>
+        <v>138</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -3440,13 +3569,13 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="B38">
         <v>6</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -3464,27 +3593,27 @@
         <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J38" t="s">
-        <v>138</v>
+        <v>297</v>
       </c>
       <c r="K38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>328</v>
+        <v>9</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -3502,21 +3631,21 @@
         <v>10</v>
       </c>
       <c r="I39" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="J39" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="B40">
         <v>6</v>
@@ -3540,65 +3669,65 @@
         <v>10</v>
       </c>
       <c r="I40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J40" t="s">
-        <v>311</v>
+        <v>138</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>90</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>57</v>
+      </c>
+      <c r="J41" t="s">
+        <v>332</v>
+      </c>
+      <c r="K41">
         <v>3</v>
       </c>
-      <c r="D41">
-        <v>2</v>
-      </c>
-      <c r="E41">
-        <v>90</v>
-      </c>
-      <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41">
-        <v>10</v>
-      </c>
-      <c r="H41">
-        <v>10</v>
-      </c>
-      <c r="I41" t="s">
-        <v>57</v>
-      </c>
-      <c r="J41" t="s">
-        <v>336</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
       <c r="L41" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -3616,27 +3745,27 @@
         <v>10</v>
       </c>
       <c r="I42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J42" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K42">
         <v>3</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>301</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -3654,27 +3783,27 @@
         <v>10</v>
       </c>
       <c r="I43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J43" t="s">
-        <v>205</v>
+        <v>336</v>
       </c>
       <c r="K43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -3692,27 +3821,27 @@
         <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="J44" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="K44">
         <v>3</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -3730,21 +3859,21 @@
         <v>10</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J45" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="B46">
         <v>6</v>
@@ -3768,21 +3897,21 @@
         <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="J46" t="s">
-        <v>140</v>
+        <v>311</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="B47">
         <v>6</v>
@@ -3809,10 +3938,10 @@
         <v>57</v>
       </c>
       <c r="J47" t="s">
-        <v>390</v>
+        <v>139</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>163</v>
@@ -3820,13 +3949,13 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -3844,21 +3973,21 @@
         <v>10</v>
       </c>
       <c r="I48" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J48" t="s">
-        <v>333</v>
+        <v>140</v>
       </c>
       <c r="K48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -3885,24 +4014,24 @@
         <v>57</v>
       </c>
       <c r="J49" t="s">
-        <v>141</v>
+        <v>390</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -3923,18 +4052,18 @@
         <v>57</v>
       </c>
       <c r="J50" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="B51">
         <v>6</v>
@@ -3949,65 +4078,74 @@
         <v>90</v>
       </c>
       <c r="F51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J51" t="s">
-        <v>336</v>
+        <v>141</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>391</v>
+        <v>85</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52">
+        <v>6</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>10</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" t="s">
+        <v>204</v>
+      </c>
+      <c r="K52">
         <v>1</v>
       </c>
-      <c r="D52">
-        <v>2</v>
-      </c>
-      <c r="E52">
-        <v>90</v>
-      </c>
-      <c r="F52">
-        <v>10</v>
-      </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-      <c r="H52">
-        <v>10</v>
-      </c>
-      <c r="I52" t="s">
-        <v>165</v>
+      <c r="L52" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -4028,18 +4166,18 @@
         <v>58</v>
       </c>
       <c r="J53" t="s">
-        <v>143</v>
+        <v>412</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -4063,27 +4201,27 @@
         <v>10</v>
       </c>
       <c r="I54" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J54" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>391</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -4101,27 +4239,18 @@
         <v>10</v>
       </c>
       <c r="I55" t="s">
-        <v>58</v>
-      </c>
-      <c r="J55" t="s">
-        <v>202</v>
-      </c>
-      <c r="K55">
-        <v>3</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B56">
         <v>6</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -4139,27 +4268,18 @@
         <v>10</v>
       </c>
       <c r="I56" t="s">
-        <v>57</v>
-      </c>
-      <c r="J56" t="s">
-        <v>202</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B57">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -4177,10 +4297,10 @@
         <v>10</v>
       </c>
       <c r="I57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J57" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -4191,13 +4311,13 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="B58">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -4218,24 +4338,24 @@
         <v>57</v>
       </c>
       <c r="J58" t="s">
-        <v>371</v>
+        <v>307</v>
       </c>
       <c r="K58">
         <v>3</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -4253,10 +4373,10 @@
         <v>10</v>
       </c>
       <c r="I59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J59" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="K59">
         <v>3</v>
@@ -4267,13 +4387,13 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>401</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -4294,10 +4414,10 @@
         <v>58</v>
       </c>
       <c r="J60" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>161</v>
@@ -4305,75 +4425,75 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="B61">
         <v>6</v>
       </c>
       <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+      <c r="E61">
+        <v>90</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>10</v>
+      </c>
+      <c r="I61" t="s">
+        <v>57</v>
+      </c>
+      <c r="J61" t="s">
+        <v>183</v>
+      </c>
+      <c r="K61">
         <v>1</v>
       </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61">
-        <v>90</v>
-      </c>
-      <c r="F61">
-        <v>10</v>
-      </c>
-      <c r="G61">
-        <v>10</v>
-      </c>
-      <c r="H61">
-        <v>10</v>
-      </c>
-      <c r="I61" t="s">
-        <v>57</v>
-      </c>
-      <c r="J61" t="s">
-        <v>358</v>
-      </c>
-      <c r="K61">
-        <v>3</v>
-      </c>
       <c r="L61" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>403</v>
+        <v>87</v>
       </c>
       <c r="B62">
         <v>6</v>
       </c>
       <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>90</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>10</v>
+      </c>
+      <c r="H62">
+        <v>10</v>
+      </c>
+      <c r="I62" t="s">
+        <v>57</v>
+      </c>
+      <c r="J62" t="s">
+        <v>371</v>
+      </c>
+      <c r="K62">
         <v>3</v>
-      </c>
-      <c r="D62">
-        <v>2</v>
-      </c>
-      <c r="E62">
-        <v>90</v>
-      </c>
-      <c r="F62">
-        <v>7</v>
-      </c>
-      <c r="G62">
-        <v>8</v>
-      </c>
-      <c r="H62">
-        <v>7</v>
-      </c>
-      <c r="I62" t="s">
-        <v>165</v>
-      </c>
-      <c r="J62" t="s">
-        <v>404</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>161</v>
@@ -4381,51 +4501,51 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="B63">
         <v>6</v>
       </c>
       <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>90</v>
+      </c>
+      <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63">
+        <v>10</v>
+      </c>
+      <c r="H63">
+        <v>10</v>
+      </c>
+      <c r="I63" t="s">
+        <v>58</v>
+      </c>
+      <c r="J63" t="s">
+        <v>414</v>
+      </c>
+      <c r="K63">
         <v>3</v>
       </c>
-      <c r="D63">
-        <v>2</v>
-      </c>
-      <c r="E63">
-        <v>90</v>
-      </c>
-      <c r="F63">
-        <v>10</v>
-      </c>
-      <c r="G63">
-        <v>10</v>
-      </c>
-      <c r="H63">
-        <v>10</v>
-      </c>
-      <c r="I63" t="s">
-        <v>165</v>
-      </c>
-      <c r="J63" t="s">
-        <v>270</v>
-      </c>
-      <c r="K63">
-        <v>1</v>
-      </c>
       <c r="L63" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -4446,53 +4566,62 @@
         <v>57</v>
       </c>
       <c r="J64" t="s">
-        <v>388</v>
+        <v>183</v>
       </c>
       <c r="K64">
         <v>3</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>374</v>
+        <v>13</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <v>90</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65">
+        <v>10</v>
+      </c>
+      <c r="H65">
+        <v>10</v>
+      </c>
+      <c r="I65" t="s">
+        <v>58</v>
+      </c>
+      <c r="J65" t="s">
+        <v>388</v>
+      </c>
+      <c r="K65">
         <v>3</v>
       </c>
-      <c r="D65">
-        <v>2</v>
-      </c>
-      <c r="E65">
-        <v>90</v>
-      </c>
-      <c r="F65">
-        <v>10</v>
-      </c>
-      <c r="G65">
-        <v>10</v>
-      </c>
-      <c r="H65">
-        <v>10</v>
-      </c>
-      <c r="I65" t="s">
-        <v>165</v>
+      <c r="L65" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>324</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -4510,27 +4639,27 @@
         <v>10</v>
       </c>
       <c r="I66" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="J66" t="s">
-        <v>184</v>
+        <v>358</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>288</v>
+        <v>402</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -4548,10 +4677,10 @@
         <v>10</v>
       </c>
       <c r="I67" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J67" t="s">
-        <v>289</v>
+        <v>403</v>
       </c>
       <c r="K67">
         <v>3</v>
@@ -4562,13 +4691,13 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -4586,10 +4715,10 @@
         <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J68" t="s">
-        <v>142</v>
+        <v>270</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -4600,13 +4729,13 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>351</v>
+        <v>14</v>
       </c>
       <c r="B69">
         <v>6</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -4627,18 +4756,18 @@
         <v>57</v>
       </c>
       <c r="J69" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="B70">
         <v>6</v>
@@ -4662,27 +4791,18 @@
         <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>57</v>
-      </c>
-      <c r="J70" t="s">
-        <v>144</v>
-      </c>
-      <c r="K70">
-        <v>2</v>
-      </c>
-      <c r="L70" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B71">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -4700,13 +4820,13 @@
         <v>10</v>
       </c>
       <c r="I71" t="s">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="J71" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="K71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>161</v>
@@ -4714,13 +4834,13 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>288</v>
       </c>
       <c r="B72">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -4738,10 +4858,10 @@
         <v>10</v>
       </c>
       <c r="I72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J72" t="s">
-        <v>240</v>
+        <v>289</v>
       </c>
       <c r="K72">
         <v>3</v>
@@ -4752,13 +4872,13 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="B73">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -4776,13 +4896,13 @@
         <v>10</v>
       </c>
       <c r="I73" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="J73" t="s">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="K73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>161</v>
@@ -4790,13 +4910,13 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>351</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -4817,10 +4937,10 @@
         <v>57</v>
       </c>
       <c r="J74" t="s">
-        <v>145</v>
+        <v>352</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>161</v>
@@ -4828,13 +4948,13 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>375</v>
+        <v>88</v>
       </c>
       <c r="B75">
         <v>6</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4852,13 +4972,13 @@
         <v>10</v>
       </c>
       <c r="I75" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J75" t="s">
-        <v>314</v>
+        <v>144</v>
       </c>
       <c r="K75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>161</v>
@@ -4866,13 +4986,13 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="B76">
         <v>6</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -4893,10 +5013,10 @@
         <v>57</v>
       </c>
       <c r="J76" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>161</v>
@@ -4904,7 +5024,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -4928,21 +5048,21 @@
         <v>10</v>
       </c>
       <c r="I77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J77" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -4966,10 +5086,10 @@
         <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="J78" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="K78">
         <v>3</v>
@@ -4980,13 +5100,13 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B79">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -5004,21 +5124,21 @@
         <v>10</v>
       </c>
       <c r="I79" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J79" t="s">
-        <v>258</v>
+        <v>415</v>
       </c>
       <c r="K79">
         <v>3</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>353</v>
+        <v>91</v>
       </c>
       <c r="B80">
         <v>6</v>
@@ -5045,10 +5165,10 @@
         <v>57</v>
       </c>
       <c r="J80" t="s">
-        <v>356</v>
+        <v>145</v>
       </c>
       <c r="K80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>161</v>
@@ -5056,13 +5176,13 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B81">
         <v>6</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -5080,21 +5200,21 @@
         <v>10</v>
       </c>
       <c r="I81" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J81" t="s">
-        <v>146</v>
+        <v>314</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -5118,27 +5238,27 @@
         <v>10</v>
       </c>
       <c r="I82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J82" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="K82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>367</v>
+        <v>262</v>
       </c>
       <c r="B83">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -5157,46 +5277,64 @@
       </c>
       <c r="I83" t="s">
         <v>57</v>
+      </c>
+      <c r="J83" t="s">
+        <v>416</v>
+      </c>
+      <c r="K83">
+        <v>3</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>405</v>
+        <v>28</v>
       </c>
       <c r="B84">
         <v>6</v>
       </c>
       <c r="C84">
+        <v>6</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>90</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+      <c r="H84">
+        <v>10</v>
+      </c>
+      <c r="I84" t="s">
+        <v>58</v>
+      </c>
+      <c r="J84" t="s">
+        <v>258</v>
+      </c>
+      <c r="K84">
         <v>1</v>
       </c>
-      <c r="D84">
-        <v>2</v>
-      </c>
-      <c r="E84">
-        <v>90</v>
-      </c>
-      <c r="F84">
-        <v>10</v>
-      </c>
-      <c r="G84">
-        <v>10</v>
-      </c>
-      <c r="H84">
-        <v>10</v>
-      </c>
-      <c r="I84" t="s">
-        <v>165</v>
+      <c r="L84" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="B85">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -5214,13 +5352,13 @@
         <v>10</v>
       </c>
       <c r="I85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J85" t="s">
-        <v>147</v>
+        <v>355</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>161</v>
@@ -5228,13 +5366,13 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="B86">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -5252,21 +5390,21 @@
         <v>10</v>
       </c>
       <c r="I86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J86" t="s">
-        <v>388</v>
+        <v>258</v>
       </c>
       <c r="K86">
         <v>3</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>353</v>
       </c>
       <c r="B87">
         <v>6</v>
@@ -5293,7 +5431,7 @@
         <v>57</v>
       </c>
       <c r="J87" t="s">
-        <v>255</v>
+        <v>356</v>
       </c>
       <c r="K87">
         <v>3</v>
@@ -5304,13 +5442,13 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>376</v>
       </c>
       <c r="B88">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -5328,27 +5466,27 @@
         <v>10</v>
       </c>
       <c r="I88" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J88" t="s">
-        <v>392</v>
+        <v>146</v>
       </c>
       <c r="K88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B89">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -5366,13 +5504,13 @@
         <v>10</v>
       </c>
       <c r="I89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J89" t="s">
-        <v>148</v>
+        <v>417</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>161</v>
@@ -5380,36 +5518,45 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>393</v>
+        <v>29</v>
       </c>
       <c r="B90">
         <v>6</v>
       </c>
       <c r="C90">
+        <v>6</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>90</v>
+      </c>
+      <c r="F90">
+        <v>10</v>
+      </c>
+      <c r="G90">
+        <v>10</v>
+      </c>
+      <c r="H90">
+        <v>10</v>
+      </c>
+      <c r="I90" t="s">
+        <v>57</v>
+      </c>
+      <c r="J90" t="s">
+        <v>146</v>
+      </c>
+      <c r="K90">
         <v>3</v>
       </c>
-      <c r="D90">
-        <v>2</v>
-      </c>
-      <c r="E90">
-        <v>90</v>
-      </c>
-      <c r="F90">
-        <v>10</v>
-      </c>
-      <c r="G90">
-        <v>10</v>
-      </c>
-      <c r="H90">
-        <v>10</v>
-      </c>
-      <c r="I90" t="s">
-        <v>165</v>
+      <c r="L90" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>298</v>
+        <v>367</v>
       </c>
       <c r="B91">
         <v>6</v>
@@ -5436,24 +5583,24 @@
         <v>57</v>
       </c>
       <c r="J91" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="K91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>404</v>
       </c>
       <c r="B92">
         <v>6</v>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -5471,27 +5618,27 @@
         <v>10</v>
       </c>
       <c r="I92" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J92" t="s">
-        <v>219</v>
+        <v>419</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B93">
         <v>6</v>
       </c>
       <c r="C93">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -5512,24 +5659,24 @@
         <v>57</v>
       </c>
       <c r="J93" t="s">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="K93">
         <v>1</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B94">
         <v>6</v>
       </c>
       <c r="C94">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -5556,12 +5703,12 @@
         <v>3</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="B95">
         <v>6</v>
@@ -5588,24 +5735,24 @@
         <v>57</v>
       </c>
       <c r="J95" t="s">
-        <v>377</v>
+        <v>255</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>406</v>
+        <v>31</v>
       </c>
       <c r="B96">
         <v>6</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -5623,18 +5770,27 @@
         <v>10</v>
       </c>
       <c r="I96" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J96" t="s">
+        <v>392</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5655,24 +5811,24 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="K97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>238</v>
+        <v>393</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5690,27 +5846,27 @@
         <v>10</v>
       </c>
       <c r="I98" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J98" t="s">
-        <v>315</v>
+        <v>418</v>
       </c>
       <c r="K98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="B99">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5728,13 +5884,13 @@
         <v>10</v>
       </c>
       <c r="I99" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J99" t="s">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>163</v>
@@ -5742,7 +5898,7 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B100">
         <v>6</v>
@@ -5766,21 +5922,21 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J100" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B101">
         <v>6</v>
@@ -5804,13 +5960,13 @@
         <v>10</v>
       </c>
       <c r="I101" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J101" t="s">
-        <v>388</v>
+        <v>271</v>
       </c>
       <c r="K101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>163</v>
@@ -5818,45 +5974,45 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102">
+        <v>6</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102">
+        <v>90</v>
+      </c>
+      <c r="F102">
+        <v>10</v>
+      </c>
+      <c r="G102">
+        <v>10</v>
+      </c>
+      <c r="H102">
+        <v>10</v>
+      </c>
+      <c r="I102" t="s">
+        <v>57</v>
+      </c>
+      <c r="J102" t="s">
+        <v>388</v>
+      </c>
+      <c r="K102">
         <v>3</v>
       </c>
-      <c r="D102">
-        <v>2</v>
-      </c>
-      <c r="E102">
-        <v>90</v>
-      </c>
-      <c r="F102">
-        <v>10</v>
-      </c>
-      <c r="G102">
-        <v>10</v>
-      </c>
-      <c r="H102">
-        <v>10</v>
-      </c>
-      <c r="I102" t="s">
-        <v>58</v>
-      </c>
-      <c r="J102" t="s">
-        <v>285</v>
-      </c>
-      <c r="K102">
-        <v>1</v>
-      </c>
       <c r="L102" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="B103">
         <v>6</v>
@@ -5883,24 +6039,24 @@
         <v>57</v>
       </c>
       <c r="J103" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="K103">
         <v>1</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>94</v>
+        <v>405</v>
       </c>
       <c r="B104">
         <v>6</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5918,21 +6074,12 @@
         <v>10</v>
       </c>
       <c r="I104" t="s">
-        <v>58</v>
-      </c>
-      <c r="J104" t="s">
-        <v>152</v>
-      </c>
-      <c r="K104">
-        <v>3</v>
-      </c>
-      <c r="L104" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B105">
         <v>6</v>
@@ -5956,27 +6103,27 @@
         <v>10</v>
       </c>
       <c r="I105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J105" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="K105">
         <v>3</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="B106">
         <v>6</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5994,27 +6141,27 @@
         <v>10</v>
       </c>
       <c r="I106" t="s">
-        <v>198</v>
+        <v>58</v>
       </c>
       <c r="J106" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K106">
         <v>3</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B107">
         <v>6</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -6032,21 +6179,21 @@
         <v>10</v>
       </c>
       <c r="I107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J107" t="s">
-        <v>272</v>
+        <v>149</v>
       </c>
       <c r="K107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B108">
         <v>6</v>
@@ -6073,7 +6220,7 @@
         <v>57</v>
       </c>
       <c r="J108" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K108">
         <v>1</v>
@@ -6084,7 +6231,7 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="B109">
         <v>6</v>
@@ -6108,27 +6255,27 @@
         <v>10</v>
       </c>
       <c r="I109" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J109" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="K109">
         <v>3</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>312</v>
+        <v>221</v>
       </c>
       <c r="B110">
         <v>6</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -6146,21 +6293,21 @@
         <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J110" t="s">
-        <v>382</v>
+        <v>285</v>
       </c>
       <c r="K110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="B111">
         <v>6</v>
@@ -6184,27 +6331,27 @@
         <v>10</v>
       </c>
       <c r="I111" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J111" t="s">
-        <v>381</v>
+        <v>304</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>420</v>
       </c>
       <c r="B112">
         <v>6</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -6222,27 +6369,27 @@
         <v>10</v>
       </c>
       <c r="I112" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J112" t="s">
-        <v>286</v>
+        <v>421</v>
       </c>
       <c r="K112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="B113">
         <v>6</v>
       </c>
       <c r="C113">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -6260,27 +6407,27 @@
         <v>10</v>
       </c>
       <c r="I113" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J113" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="K113">
         <v>3</v>
       </c>
       <c r="L113" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="B114">
         <v>6</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -6298,10 +6445,10 @@
         <v>10</v>
       </c>
       <c r="I114" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J114" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="K114">
         <v>3</v>
@@ -6312,7 +6459,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="B115">
         <v>6</v>
@@ -6336,21 +6483,21 @@
         <v>10</v>
       </c>
       <c r="I115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J115" t="s">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="K115">
         <v>3</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B116">
         <v>6</v>
@@ -6374,27 +6521,27 @@
         <v>10</v>
       </c>
       <c r="I116" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="J116" t="s">
-        <v>194</v>
+        <v>316</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B117">
         <v>6</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -6412,21 +6559,21 @@
         <v>10</v>
       </c>
       <c r="I117" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J117" t="s">
-        <v>154</v>
+        <v>272</v>
       </c>
       <c r="K117">
         <v>3</v>
       </c>
       <c r="L117" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -6453,18 +6600,18 @@
         <v>57</v>
       </c>
       <c r="J118" t="s">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="K118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>226</v>
+        <v>354</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -6488,10 +6635,10 @@
         <v>10</v>
       </c>
       <c r="I119" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J119" t="s">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="K119">
         <v>3</v>
@@ -6502,7 +6649,7 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="B120">
         <v>6</v>
@@ -6529,24 +6676,24 @@
         <v>57</v>
       </c>
       <c r="J120" t="s">
-        <v>155</v>
+        <v>382</v>
       </c>
       <c r="K120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>35</v>
+        <v>423</v>
       </c>
       <c r="B121">
         <v>6</v>
       </c>
       <c r="C121">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -6564,27 +6711,27 @@
         <v>10</v>
       </c>
       <c r="I121" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="J121" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="K121">
         <v>3</v>
       </c>
       <c r="L121" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="B122">
         <v>6</v>
       </c>
       <c r="C122">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6602,27 +6749,27 @@
         <v>10</v>
       </c>
       <c r="I122" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J122" t="s">
-        <v>295</v>
+        <v>381</v>
       </c>
       <c r="K122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L122" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="B123">
         <v>6</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -6640,10 +6787,10 @@
         <v>10</v>
       </c>
       <c r="I123" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J123" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -6654,7 +6801,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>253</v>
+        <v>337</v>
       </c>
       <c r="B124">
         <v>6</v>
@@ -6678,10 +6825,10 @@
         <v>10</v>
       </c>
       <c r="I124" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J124" t="s">
-        <v>155</v>
+        <v>338</v>
       </c>
       <c r="K124">
         <v>3</v>
@@ -6692,13 +6839,13 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="B125">
         <v>6</v>
       </c>
       <c r="C125">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -6716,13 +6863,13 @@
         <v>10</v>
       </c>
       <c r="I125" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="J125" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>162</v>
@@ -6730,13 +6877,13 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="B126">
         <v>6</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D126">
         <v>2</v>
@@ -6757,24 +6904,24 @@
         <v>57</v>
       </c>
       <c r="J126" t="s">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="K126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L126" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B127">
         <v>6</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -6795,18 +6942,18 @@
         <v>58</v>
       </c>
       <c r="J127" t="s">
-        <v>388</v>
+        <v>194</v>
       </c>
       <c r="K127">
         <v>3</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -6830,21 +6977,21 @@
         <v>10</v>
       </c>
       <c r="I128" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J128" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="K128">
         <v>3</v>
       </c>
       <c r="L128" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B129">
         <v>6</v>
@@ -6868,27 +7015,27 @@
         <v>10</v>
       </c>
       <c r="I129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J129" t="s">
-        <v>394</v>
+        <v>235</v>
       </c>
       <c r="K129">
         <v>3</v>
       </c>
       <c r="L129" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>407</v>
+        <v>226</v>
       </c>
       <c r="B130">
         <v>6</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D130">
         <v>2</v>
@@ -6897,60 +7044,60 @@
         <v>90</v>
       </c>
       <c r="F130">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G130">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H130">
         <v>10</v>
       </c>
       <c r="I130" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="J130" t="s">
-        <v>408</v>
+        <v>158</v>
       </c>
       <c r="K130">
         <v>3</v>
       </c>
       <c r="L130" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>379</v>
+        <v>35</v>
       </c>
       <c r="B131">
         <v>6</v>
       </c>
       <c r="C131">
+        <v>6</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131">
+        <v>90</v>
+      </c>
+      <c r="F131">
+        <v>10</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>10</v>
+      </c>
+      <c r="I131" t="s">
+        <v>57</v>
+      </c>
+      <c r="J131" t="s">
+        <v>155</v>
+      </c>
+      <c r="K131">
         <v>1</v>
-      </c>
-      <c r="D131">
-        <v>2</v>
-      </c>
-      <c r="E131">
-        <v>90</v>
-      </c>
-      <c r="F131">
-        <v>10</v>
-      </c>
-      <c r="G131">
-        <v>10</v>
-      </c>
-      <c r="H131">
-        <v>10</v>
-      </c>
-      <c r="I131" t="s">
-        <v>165</v>
-      </c>
-      <c r="J131" t="s">
-        <v>409</v>
-      </c>
-      <c r="K131">
-        <v>2</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>162</v>
@@ -6958,10 +7105,10 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="B132">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C132">
         <v>6</v>
@@ -6970,94 +7117,112 @@
         <v>2</v>
       </c>
       <c r="E132">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G132">
         <v>10</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I132" t="s">
         <v>58</v>
       </c>
       <c r="J132" t="s">
-        <v>222</v>
+        <v>388</v>
       </c>
       <c r="K132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L132" s="8" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>368</v>
+        <v>95</v>
       </c>
       <c r="B133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D133">
         <v>2</v>
       </c>
       <c r="E133">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F133">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G133">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I133" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J133" t="s">
+        <v>295</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C134">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D134">
         <v>2</v>
       </c>
       <c r="E134">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F134">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G134">
         <v>10</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I134" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J134" t="s">
+        <v>295</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="B135">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C135">
         <v>6</v>
@@ -7066,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="E135">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F135">
         <v>10</v>
@@ -7075,16 +7240,16 @@
         <v>10</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I135" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="J135" t="s">
-        <v>299</v>
+        <v>155</v>
       </c>
       <c r="K135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L135" s="8" t="s">
         <v>162</v>
@@ -7092,10 +7257,10 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>230</v>
+        <v>378</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C136">
         <v>6</v>
@@ -7104,27 +7269,36 @@
         <v>2</v>
       </c>
       <c r="E136">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F136">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G136">
         <v>10</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I136" t="s">
         <v>165</v>
       </c>
+      <c r="J136" t="s">
+        <v>155</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C137">
         <v>6</v>
@@ -7133,65 +7307,83 @@
         <v>2</v>
       </c>
       <c r="E137">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F137">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G137">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I137" t="s">
         <v>165</v>
       </c>
+      <c r="J137" t="s">
+        <v>425</v>
+      </c>
+      <c r="K137">
+        <v>3</v>
+      </c>
+      <c r="L137" s="8" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D138">
         <v>2</v>
       </c>
       <c r="E138">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F138">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G138">
         <v>10</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I138" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="J138" t="s">
+        <v>195</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="B139">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D139">
         <v>2</v>
       </c>
       <c r="E139">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F139">
         <v>10</v>
@@ -7200,18 +7392,27 @@
         <v>10</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I139" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J139" t="s">
+        <v>388</v>
+      </c>
+      <c r="K139">
+        <v>3</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>300</v>
+        <v>37</v>
       </c>
       <c r="B140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C140">
         <v>6</v>
@@ -7220,27 +7421,36 @@
         <v>2</v>
       </c>
       <c r="E140">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F140">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G140">
         <v>10</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I140" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J140" t="s">
+        <v>254</v>
+      </c>
+      <c r="K140">
+        <v>3</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C141">
         <v>6</v>
@@ -7249,36 +7459,45 @@
         <v>2</v>
       </c>
       <c r="E141">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F141">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G141">
         <v>10</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I141" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J141" t="s">
+        <v>394</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>196</v>
+        <v>406</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D142">
         <v>2</v>
       </c>
       <c r="E142">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F142">
         <v>10</v>
@@ -7287,44 +7506,62 @@
         <v>10</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I142" t="s">
-        <v>57</v>
+        <v>165</v>
+      </c>
+      <c r="J142" t="s">
+        <v>407</v>
+      </c>
+      <c r="K142">
+        <v>3</v>
+      </c>
+      <c r="L142" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>206</v>
+        <v>379</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F143">
         <v>10</v>
       </c>
       <c r="G143">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I143" t="s">
         <v>57</v>
+      </c>
+      <c r="J143" t="s">
+        <v>408</v>
+      </c>
+      <c r="K143">
+        <v>3</v>
+      </c>
+      <c r="L143" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B144">
         <v>5</v>
@@ -7348,18 +7585,27 @@
         <v>0</v>
       </c>
       <c r="I144" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J144" t="s">
+        <v>222</v>
+      </c>
+      <c r="K144">
+        <v>1</v>
+      </c>
+      <c r="L144" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>182</v>
+        <v>368</v>
       </c>
       <c r="B145">
         <v>5</v>
       </c>
       <c r="C145">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -7368,21 +7614,21 @@
         <v>80</v>
       </c>
       <c r="F145">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>192</v>
+        <v>334</v>
       </c>
       <c r="B146">
         <v>5</v>
@@ -7406,18 +7652,18 @@
         <v>0</v>
       </c>
       <c r="I146" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>227</v>
+        <v>426</v>
       </c>
       <c r="B147">
         <v>5</v>
       </c>
       <c r="C147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D147">
         <v>2</v>
@@ -7435,12 +7681,12 @@
         <v>0</v>
       </c>
       <c r="I147" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B148">
         <v>5</v>
@@ -7458,7 +7704,7 @@
         <v>10</v>
       </c>
       <c r="G148">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H148">
         <v>0</v>
@@ -7467,18 +7713,18 @@
         <v>57</v>
       </c>
       <c r="J148" t="s">
-        <v>137</v>
+        <v>299</v>
       </c>
       <c r="K148">
         <v>1</v>
       </c>
       <c r="L148" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>317</v>
+        <v>230</v>
       </c>
       <c r="B149">
         <v>5</v>
@@ -7502,12 +7748,12 @@
         <v>0</v>
       </c>
       <c r="I149" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="B150">
         <v>5</v>
@@ -7531,12 +7777,12 @@
         <v>0</v>
       </c>
       <c r="I150" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -7554,7 +7800,7 @@
         <v>7</v>
       </c>
       <c r="G151">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H151">
         <v>0</v>
@@ -7565,7 +7811,7 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B152">
         <v>5</v>
@@ -7583,7 +7829,7 @@
         <v>10</v>
       </c>
       <c r="G152">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -7594,13 +7840,13 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>256</v>
+        <v>427</v>
       </c>
       <c r="B153">
         <v>5</v>
       </c>
       <c r="C153">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -7609,7 +7855,7 @@
         <v>80</v>
       </c>
       <c r="F153">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G153">
         <v>10</v>
@@ -7623,7 +7869,7 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>101</v>
+        <v>300</v>
       </c>
       <c r="B154">
         <v>5</v>
@@ -7652,13 +7898,13 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>428</v>
       </c>
       <c r="B155">
         <v>5</v>
       </c>
       <c r="C155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -7667,10 +7913,10 @@
         <v>80</v>
       </c>
       <c r="F155">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G155">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H155">
         <v>0</v>
@@ -7681,7 +7927,7 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -7705,12 +7951,12 @@
         <v>0</v>
       </c>
       <c r="I156" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="B157">
         <v>5</v>
@@ -7725,7 +7971,7 @@
         <v>80</v>
       </c>
       <c r="F157">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G157">
         <v>10</v>
@@ -7734,12 +7980,21 @@
         <v>0</v>
       </c>
       <c r="I157" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J157" t="s">
+        <v>396</v>
+      </c>
+      <c r="K157">
+        <v>3</v>
+      </c>
+      <c r="L157" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>260</v>
+        <v>429</v>
       </c>
       <c r="B158">
         <v>5</v>
@@ -7754,7 +8009,7 @@
         <v>80</v>
       </c>
       <c r="F158">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G158">
         <v>10</v>
@@ -7763,18 +8018,18 @@
         <v>0</v>
       </c>
       <c r="I158" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="B159">
         <v>5</v>
       </c>
       <c r="C159">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -7797,7 +8052,7 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="B160">
         <v>5</v>
@@ -7812,10 +8067,10 @@
         <v>80</v>
       </c>
       <c r="F160">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G160">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H160">
         <v>0</v>
@@ -7826,7 +8081,7 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="B161">
         <v>5</v>
@@ -7853,7 +8108,7 @@
         <v>57</v>
       </c>
       <c r="J161" t="s">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="K161">
         <v>3</v>
@@ -7864,7 +8119,7 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="B162">
         <v>5</v>
@@ -7879,7 +8134,7 @@
         <v>80</v>
       </c>
       <c r="F162">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G162">
         <v>10</v>
@@ -7893,7 +8148,7 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>105</v>
+        <v>227</v>
       </c>
       <c r="B163">
         <v>5</v>
@@ -7917,21 +8172,12 @@
         <v>0</v>
       </c>
       <c r="I163" t="s">
-        <v>57</v>
-      </c>
-      <c r="J163" t="s">
-        <v>136</v>
-      </c>
-      <c r="K163">
-        <v>1</v>
-      </c>
-      <c r="L163" s="8" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
     </row>
     <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="B164">
         <v>5</v>
@@ -7946,21 +8192,30 @@
         <v>80</v>
       </c>
       <c r="F164">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G164">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164" t="s">
         <v>57</v>
+      </c>
+      <c r="J164" t="s">
+        <v>137</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>242</v>
+        <v>317</v>
       </c>
       <c r="B165">
         <v>5</v>
@@ -7975,27 +8230,27 @@
         <v>80</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G165">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="B166">
         <v>5</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D166">
         <v>2</v>
@@ -8018,7 +8273,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B167">
         <v>5</v>
@@ -8047,7 +8302,7 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>106</v>
+        <v>430</v>
       </c>
       <c r="B168">
         <v>5</v>
@@ -8062,21 +8317,21 @@
         <v>80</v>
       </c>
       <c r="F168">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G168">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="B169">
         <v>5</v>
@@ -8100,18 +8355,18 @@
         <v>0</v>
       </c>
       <c r="I169" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B170">
         <v>5</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D170">
         <v>2</v>
@@ -8123,7 +8378,7 @@
         <v>10</v>
       </c>
       <c r="G170">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -8134,13 +8389,13 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>361</v>
+        <v>431</v>
       </c>
       <c r="B171">
         <v>5</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D171">
         <v>2</v>
@@ -8152,7 +8407,7 @@
         <v>7</v>
       </c>
       <c r="G171">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H171">
         <v>0</v>
@@ -8163,7 +8418,7 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>186</v>
+        <v>101</v>
       </c>
       <c r="B172">
         <v>5</v>
@@ -8178,10 +8433,10 @@
         <v>80</v>
       </c>
       <c r="F172">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G172">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -8192,7 +8447,7 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>107</v>
+        <v>318</v>
       </c>
       <c r="B173">
         <v>5</v>
@@ -8207,7 +8462,7 @@
         <v>80</v>
       </c>
       <c r="F173">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G173">
         <v>10</v>
@@ -8216,21 +8471,12 @@
         <v>0</v>
       </c>
       <c r="I173" t="s">
-        <v>57</v>
-      </c>
-      <c r="J173" t="s">
-        <v>144</v>
-      </c>
-      <c r="K173">
-        <v>3</v>
-      </c>
-      <c r="L173" s="8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>108</v>
+        <v>432</v>
       </c>
       <c r="B174">
         <v>5</v>
@@ -8245,21 +8491,21 @@
         <v>80</v>
       </c>
       <c r="F174">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G174">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>302</v>
+        <v>433</v>
       </c>
       <c r="B175">
         <v>5</v>
@@ -8277,18 +8523,18 @@
         <v>7</v>
       </c>
       <c r="G175">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176" spans="1:12">
       <c r="A176" t="s">
-        <v>214</v>
+        <v>319</v>
       </c>
       <c r="B176">
         <v>5</v>
@@ -8303,7 +8549,7 @@
         <v>80</v>
       </c>
       <c r="F176">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G176">
         <v>10</v>
@@ -8313,20 +8559,11 @@
       </c>
       <c r="I176" t="s">
         <v>57</v>
-      </c>
-      <c r="J176" t="s">
-        <v>184</v>
-      </c>
-      <c r="K176">
-        <v>3</v>
-      </c>
-      <c r="L176" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="177" spans="1:12">
       <c r="A177" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="B177">
         <v>5</v>
@@ -8355,7 +8592,7 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" t="s">
-        <v>362</v>
+        <v>260</v>
       </c>
       <c r="B178">
         <v>5</v>
@@ -8373,7 +8610,7 @@
         <v>7</v>
       </c>
       <c r="G178">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H178">
         <v>0</v>
@@ -8384,13 +8621,13 @@
     </row>
     <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="B179">
         <v>5</v>
       </c>
       <c r="C179">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -8413,7 +8650,7 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="B180">
         <v>5</v>
@@ -8442,7 +8679,7 @@
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B181">
         <v>5</v>
@@ -8457,7 +8694,7 @@
         <v>80</v>
       </c>
       <c r="F181">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G181">
         <v>10</v>
@@ -8466,12 +8703,21 @@
         <v>0</v>
       </c>
       <c r="I181" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J181" t="s">
+        <v>296</v>
+      </c>
+      <c r="K181">
+        <v>3</v>
+      </c>
+      <c r="L181" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="182" spans="1:12">
       <c r="A182" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B182">
         <v>5</v>
@@ -8495,21 +8741,21 @@
         <v>0</v>
       </c>
       <c r="I182" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J182" t="s">
-        <v>157</v>
+        <v>297</v>
       </c>
       <c r="K182">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L182" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="183" spans="1:12">
       <c r="A183" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B183">
         <v>5</v>
@@ -8535,10 +8781,19 @@
       <c r="I183" t="s">
         <v>57</v>
       </c>
+      <c r="J183" t="s">
+        <v>136</v>
+      </c>
+      <c r="K183">
+        <v>1</v>
+      </c>
+      <c r="L183" s="8" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="184" spans="1:12">
       <c r="A184" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="B184">
         <v>5</v>
@@ -8553,30 +8808,21 @@
         <v>80</v>
       </c>
       <c r="F184">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G184">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184" t="s">
         <v>57</v>
-      </c>
-      <c r="J184" t="s">
-        <v>143</v>
-      </c>
-      <c r="K184">
-        <v>1</v>
-      </c>
-      <c r="L184" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="185" spans="1:12">
       <c r="A185" t="s">
-        <v>229</v>
+        <v>434</v>
       </c>
       <c r="B185">
         <v>5</v>
@@ -8591,7 +8837,7 @@
         <v>80</v>
       </c>
       <c r="F185">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G185">
         <v>10</v>
@@ -8600,12 +8846,12 @@
         <v>0</v>
       </c>
       <c r="I185" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="B186">
         <v>5</v>
@@ -8623,24 +8869,24 @@
         <v>10</v>
       </c>
       <c r="G186">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H186">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I186" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:12">
       <c r="A187" t="s">
-        <v>113</v>
+        <v>251</v>
       </c>
       <c r="B187">
         <v>5</v>
       </c>
       <c r="C187">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -8663,13 +8909,13 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="B188">
         <v>5</v>
       </c>
       <c r="C188">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D188">
         <v>2</v>
@@ -8692,7 +8938,7 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" t="s">
-        <v>363</v>
+        <v>106</v>
       </c>
       <c r="B189">
         <v>5</v>
@@ -8707,7 +8953,7 @@
         <v>80</v>
       </c>
       <c r="F189">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G189">
         <v>7</v>
@@ -8716,12 +8962,12 @@
         <v>0</v>
       </c>
       <c r="I189" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B190">
         <v>5</v>
@@ -8736,10 +8982,10 @@
         <v>80</v>
       </c>
       <c r="F190">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G190">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H190">
         <v>0</v>
@@ -8750,7 +8996,7 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" t="s">
-        <v>276</v>
+        <v>435</v>
       </c>
       <c r="B191">
         <v>5</v>
@@ -8774,18 +9020,18 @@
         <v>0</v>
       </c>
       <c r="I191" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:12">
       <c r="A192" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B192">
         <v>5</v>
       </c>
       <c r="C192">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -8794,27 +9040,27 @@
         <v>80</v>
       </c>
       <c r="F192">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G192">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>228</v>
+        <v>361</v>
       </c>
       <c r="B193">
         <v>5</v>
       </c>
       <c r="C193">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D193">
         <v>2</v>
@@ -8826,7 +9072,7 @@
         <v>7</v>
       </c>
       <c r="G193">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -8837,7 +9083,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="B194">
         <v>5</v>
@@ -8852,36 +9098,27 @@
         <v>80</v>
       </c>
       <c r="F194">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G194">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194" t="s">
         <v>57</v>
-      </c>
-      <c r="J194" t="s">
-        <v>149</v>
-      </c>
-      <c r="K194">
-        <v>1</v>
-      </c>
-      <c r="L194" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="195" spans="1:12">
       <c r="A195" t="s">
-        <v>308</v>
+        <v>107</v>
       </c>
       <c r="B195">
         <v>5</v>
       </c>
       <c r="C195">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -8890,7 +9127,7 @@
         <v>80</v>
       </c>
       <c r="F195">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G195">
         <v>10</v>
@@ -8899,12 +9136,21 @@
         <v>0</v>
       </c>
       <c r="I195" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J195" t="s">
+        <v>144</v>
+      </c>
+      <c r="K195">
+        <v>3</v>
+      </c>
+      <c r="L195" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B196">
         <v>5</v>
@@ -8919,7 +9165,7 @@
         <v>80</v>
       </c>
       <c r="F196">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G196">
         <v>10</v>
@@ -8928,21 +9174,12 @@
         <v>0</v>
       </c>
       <c r="I196" t="s">
-        <v>58</v>
-      </c>
-      <c r="J196" t="s">
-        <v>364</v>
-      </c>
-      <c r="K196">
-        <v>3</v>
-      </c>
-      <c r="L196" s="8" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
     </row>
     <row r="197" spans="1:12">
       <c r="A197" t="s">
-        <v>117</v>
+        <v>302</v>
       </c>
       <c r="B197">
         <v>5</v>
@@ -8957,27 +9194,27 @@
         <v>80</v>
       </c>
       <c r="F197">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G197">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H197">
         <v>0</v>
       </c>
       <c r="I197" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>118</v>
+        <v>436</v>
       </c>
       <c r="B198">
         <v>5</v>
       </c>
       <c r="C198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D198">
         <v>2</v>
@@ -8986,21 +9223,30 @@
         <v>80</v>
       </c>
       <c r="F198">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G198">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H198">
         <v>0</v>
       </c>
       <c r="I198" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="J198" t="s">
+        <v>352</v>
+      </c>
+      <c r="K198">
+        <v>1</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
       <c r="B199">
         <v>5</v>
@@ -9015,7 +9261,7 @@
         <v>80</v>
       </c>
       <c r="F199">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G199">
         <v>10</v>
@@ -9026,10 +9272,19 @@
       <c r="I199" t="s">
         <v>58</v>
       </c>
+      <c r="J199" t="s">
+        <v>184</v>
+      </c>
+      <c r="K199">
+        <v>3</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="200" spans="1:12">
       <c r="A200" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="B200">
         <v>5</v>
@@ -9058,13 +9313,13 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" t="s">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="B201">
         <v>5</v>
       </c>
       <c r="C201">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D201">
         <v>2</v>
@@ -9087,13 +9342,13 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" t="s">
-        <v>215</v>
+        <v>362</v>
       </c>
       <c r="B202">
         <v>5</v>
       </c>
       <c r="C202">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D202">
         <v>2</v>
@@ -9105,18 +9360,18 @@
         <v>7</v>
       </c>
       <c r="G202">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H202">
         <v>0</v>
       </c>
       <c r="I202" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203" spans="1:12">
       <c r="A203" t="s">
-        <v>121</v>
+        <v>274</v>
       </c>
       <c r="B203">
         <v>5</v>
@@ -9131,7 +9386,7 @@
         <v>80</v>
       </c>
       <c r="F203">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G203">
         <v>10</v>
@@ -9140,12 +9395,12 @@
         <v>0</v>
       </c>
       <c r="I203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="B204">
         <v>5</v>
@@ -9169,12 +9424,12 @@
         <v>0</v>
       </c>
       <c r="I204" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="205" spans="1:12">
       <c r="A205" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B205">
         <v>5</v>
@@ -9198,21 +9453,12 @@
         <v>0</v>
       </c>
       <c r="I205" t="s">
-        <v>57</v>
-      </c>
-      <c r="J205" t="s">
-        <v>153</v>
-      </c>
-      <c r="K205">
-        <v>1</v>
-      </c>
-      <c r="L205" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>123</v>
+        <v>438</v>
       </c>
       <c r="B206">
         <v>5</v>
@@ -9227,10 +9473,10 @@
         <v>80</v>
       </c>
       <c r="F206">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G206">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -9241,7 +9487,7 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B207">
         <v>5</v>
@@ -9256,7 +9502,7 @@
         <v>80</v>
       </c>
       <c r="F207">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G207">
         <v>10</v>
@@ -9265,21 +9511,21 @@
         <v>0</v>
       </c>
       <c r="I207" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J207" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K207">
         <v>1</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="B208">
         <v>5</v>
@@ -9303,12 +9549,12 @@
         <v>0</v>
       </c>
       <c r="I208" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>331</v>
+        <v>112</v>
       </c>
       <c r="B209">
         <v>5</v>
@@ -9323,21 +9569,30 @@
         <v>80</v>
       </c>
       <c r="F209">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G209">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H209">
         <v>0</v>
       </c>
       <c r="I209" t="s">
-        <v>165</v>
+        <v>57</v>
+      </c>
+      <c r="J209" t="s">
+        <v>143</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="B210">
         <v>5</v>
@@ -9366,7 +9621,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="B211">
         <v>5</v>
@@ -9381,21 +9636,30 @@
         <v>80</v>
       </c>
       <c r="F211">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G211">
         <v>10</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I211" t="s">
-        <v>165</v>
+        <v>198</v>
+      </c>
+      <c r="J211" t="s">
+        <v>416</v>
+      </c>
+      <c r="K211">
+        <v>3</v>
+      </c>
+      <c r="L211" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B212">
         <v>5</v>
@@ -9410,7 +9674,7 @@
         <v>80</v>
       </c>
       <c r="F212">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G212">
         <v>10</v>
@@ -9420,20 +9684,11 @@
       </c>
       <c r="I212" t="s">
         <v>57</v>
-      </c>
-      <c r="J212" t="s">
-        <v>154</v>
-      </c>
-      <c r="K212">
-        <v>1</v>
-      </c>
-      <c r="L212" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="213" spans="1:12">
       <c r="A213" t="s">
-        <v>127</v>
+        <v>290</v>
       </c>
       <c r="B213">
         <v>5</v>
@@ -9448,7 +9703,7 @@
         <v>80</v>
       </c>
       <c r="F213">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G213">
         <v>10</v>
@@ -9458,26 +9713,17 @@
       </c>
       <c r="I213" t="s">
         <v>57</v>
-      </c>
-      <c r="J213" t="s">
-        <v>158</v>
-      </c>
-      <c r="K213">
-        <v>1</v>
-      </c>
-      <c r="L213" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>128</v>
+        <v>439</v>
       </c>
       <c r="B214">
         <v>5</v>
       </c>
       <c r="C214">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D214">
         <v>2</v>
@@ -9486,30 +9732,21 @@
         <v>80</v>
       </c>
       <c r="F214">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G214">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H214">
         <v>0</v>
       </c>
       <c r="I214" t="s">
         <v>57</v>
-      </c>
-      <c r="J214" t="s">
-        <v>155</v>
-      </c>
-      <c r="K214">
-        <v>1</v>
-      </c>
-      <c r="L214" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>363</v>
       </c>
       <c r="B215">
         <v>5</v>
@@ -9524,10 +9761,10 @@
         <v>80</v>
       </c>
       <c r="F215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G215">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -9538,7 +9775,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B216">
         <v>5</v>
@@ -9553,36 +9790,27 @@
         <v>80</v>
       </c>
       <c r="F216">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G216">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H216">
         <v>0</v>
       </c>
       <c r="I216" t="s">
         <v>57</v>
-      </c>
-      <c r="J216" t="s">
-        <v>158</v>
-      </c>
-      <c r="K216">
-        <v>1</v>
-      </c>
-      <c r="L216" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="B217">
         <v>5</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D217">
         <v>2</v>
@@ -9591,7 +9819,7 @@
         <v>80</v>
       </c>
       <c r="F217">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G217">
         <v>10</v>
@@ -9605,13 +9833,13 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" t="s">
-        <v>130</v>
+        <v>441</v>
       </c>
       <c r="B218">
         <v>5</v>
       </c>
       <c r="C218">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D218">
         <v>2</v>
@@ -9620,7 +9848,7 @@
         <v>80</v>
       </c>
       <c r="F218">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G218">
         <v>10</v>
@@ -9629,12 +9857,12 @@
         <v>0</v>
       </c>
       <c r="I218" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:12">
       <c r="A219" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
       <c r="B219">
         <v>5</v>
@@ -9649,30 +9877,21 @@
         <v>80</v>
       </c>
       <c r="F219">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G219">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H219">
         <v>0</v>
       </c>
       <c r="I219" t="s">
-        <v>58</v>
-      </c>
-      <c r="J219" t="s">
-        <v>343</v>
-      </c>
-      <c r="K219">
-        <v>1</v>
-      </c>
-      <c r="L219" s="8" t="s">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="220" spans="1:12">
       <c r="A220" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="B220">
         <v>5</v>
@@ -9696,12 +9915,12 @@
         <v>0</v>
       </c>
       <c r="I220" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="221" spans="1:12">
       <c r="A221" t="s">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="B221">
         <v>5</v>
@@ -9725,18 +9944,18 @@
         <v>0</v>
       </c>
       <c r="I221" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222" spans="1:12">
       <c r="A222" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B222">
         <v>5</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D222">
         <v>2</v>
@@ -9754,18 +9973,27 @@
         <v>0</v>
       </c>
       <c r="I222" t="s">
-        <v>165</v>
+        <v>58</v>
+      </c>
+      <c r="J222" t="s">
+        <v>149</v>
+      </c>
+      <c r="K222">
+        <v>3</v>
+      </c>
+      <c r="L222" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="223" spans="1:12">
       <c r="A223" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B223">
         <v>5</v>
       </c>
       <c r="C223">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D223">
         <v>2</v>
@@ -9788,7 +10016,7 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" t="s">
-        <v>200</v>
+        <v>442</v>
       </c>
       <c r="B224">
         <v>5</v>
@@ -9812,15 +10040,15 @@
         <v>0</v>
       </c>
       <c r="I224" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:12">
       <c r="A225" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="B225">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C225">
         <v>6</v>
@@ -9829,7 +10057,7 @@
         <v>2</v>
       </c>
       <c r="E225">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F225">
         <v>10</v>
@@ -9841,27 +10069,36 @@
         <v>0</v>
       </c>
       <c r="I225" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J225" t="s">
+        <v>364</v>
+      </c>
+      <c r="K225">
+        <v>3</v>
+      </c>
+      <c r="L225" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="226" spans="1:12">
       <c r="A226" t="s">
-        <v>188</v>
+        <v>443</v>
       </c>
       <c r="B226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C226">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D226">
         <v>2</v>
       </c>
       <c r="E226">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F226">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G226">
         <v>10</v>
@@ -9870,15 +10107,15 @@
         <v>0</v>
       </c>
       <c r="I226" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:12">
       <c r="A227" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="B227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C227">
         <v>6</v>
@@ -9887,13 +10124,13 @@
         <v>2</v>
       </c>
       <c r="E227">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F227">
         <v>10</v>
       </c>
       <c r="G227">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H227">
         <v>0</v>
@@ -9901,22 +10138,13 @@
       <c r="I227" t="s">
         <v>58</v>
       </c>
-      <c r="J227" t="s">
-        <v>299</v>
-      </c>
-      <c r="K227">
-        <v>3</v>
-      </c>
-      <c r="L227" s="8" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="228" spans="1:12">
       <c r="A228" t="s">
-        <v>325</v>
+        <v>118</v>
       </c>
       <c r="B228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C228">
         <v>6</v>
@@ -9925,7 +10153,7 @@
         <v>2</v>
       </c>
       <c r="E228">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F228">
         <v>7</v>
@@ -9937,15 +10165,15 @@
         <v>0</v>
       </c>
       <c r="I228" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:12">
       <c r="A229" t="s">
-        <v>63</v>
+        <v>444</v>
       </c>
       <c r="B229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C229">
         <v>6</v>
@@ -9954,13 +10182,13 @@
         <v>2</v>
       </c>
       <c r="E229">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F229">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G229">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -9968,22 +10196,13 @@
       <c r="I229" t="s">
         <v>165</v>
       </c>
-      <c r="J229" t="s">
-        <v>159</v>
-      </c>
-      <c r="K229">
-        <v>1</v>
-      </c>
-      <c r="L229" s="8" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="230" spans="1:12">
       <c r="A230" t="s">
-        <v>322</v>
+        <v>119</v>
       </c>
       <c r="B230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C230">
         <v>6</v>
@@ -9992,51 +10211,42 @@
         <v>2</v>
       </c>
       <c r="E230">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F230">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G230">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>57</v>
-      </c>
-      <c r="J230" t="s">
-        <v>347</v>
-      </c>
-      <c r="K230">
-        <v>1</v>
-      </c>
-      <c r="L230" s="8" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:12">
       <c r="A231" t="s">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="B231">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D231">
         <v>2</v>
       </c>
       <c r="E231">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F231">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G231">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H231">
         <v>0</v>
@@ -10047,10 +10257,10 @@
     </row>
     <row r="232" spans="1:12">
       <c r="A232" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="B232">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C232">
         <v>6</v>
@@ -10059,7 +10269,7 @@
         <v>2</v>
       </c>
       <c r="E232">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F232">
         <v>7</v>
@@ -10076,10 +10286,10 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" t="s">
-        <v>344</v>
+        <v>445</v>
       </c>
       <c r="B233">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C233">
         <v>6</v>
@@ -10088,56 +10298,56 @@
         <v>2</v>
       </c>
       <c r="E233">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F233">
         <v>7</v>
       </c>
       <c r="G233">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>64</v>
+        <v>215</v>
       </c>
       <c r="B234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C234">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D234">
         <v>2</v>
       </c>
       <c r="E234">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F234">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G234">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H234">
         <v>0</v>
       </c>
       <c r="I234" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="235" spans="1:12">
       <c r="A235" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="B235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C235">
         <v>6</v>
@@ -10146,10 +10356,10 @@
         <v>2</v>
       </c>
       <c r="E235">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F235">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G235">
         <v>10</v>
@@ -10158,44 +10368,44 @@
         <v>0</v>
       </c>
       <c r="I235" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:12">
       <c r="A236" t="s">
-        <v>211</v>
+        <v>320</v>
       </c>
       <c r="B236">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D236">
         <v>2</v>
       </c>
       <c r="E236">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F236">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G236">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H236">
         <v>0</v>
       </c>
       <c r="I236" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
     </row>
     <row r="237" spans="1:12">
       <c r="A237" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="B237">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C237">
         <v>6</v>
@@ -10204,27 +10414,36 @@
         <v>2</v>
       </c>
       <c r="E237">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F237">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G237">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H237">
         <v>0</v>
       </c>
       <c r="I237" t="s">
         <v>57</v>
+      </c>
+      <c r="J237" t="s">
+        <v>153</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="238" spans="1:12">
       <c r="A238" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="B238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C238">
         <v>6</v>
@@ -10233,10 +10452,10 @@
         <v>2</v>
       </c>
       <c r="E238">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F238">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -10245,15 +10464,15 @@
         <v>0</v>
       </c>
       <c r="I238" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="239" spans="1:12">
       <c r="A239" t="s">
-        <v>323</v>
+        <v>124</v>
       </c>
       <c r="B239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C239">
         <v>6</v>
@@ -10262,7 +10481,7 @@
         <v>2</v>
       </c>
       <c r="E239">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F239">
         <v>7</v>
@@ -10275,14 +10494,23 @@
       </c>
       <c r="I239" t="s">
         <v>57</v>
+      </c>
+      <c r="J239" t="s">
+        <v>153</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="240" spans="1:12">
       <c r="A240" t="s">
-        <v>346</v>
+        <v>187</v>
       </c>
       <c r="B240">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C240">
         <v>6</v>
@@ -10291,7 +10519,7 @@
         <v>2</v>
       </c>
       <c r="E240">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F240">
         <v>7</v>
@@ -10303,15 +10531,15 @@
         <v>0</v>
       </c>
       <c r="I240" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="241" spans="1:12">
       <c r="A241" t="s">
-        <v>66</v>
+        <v>331</v>
       </c>
       <c r="B241">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C241">
         <v>6</v>
@@ -10320,10 +10548,10 @@
         <v>2</v>
       </c>
       <c r="E241">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F241">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G241">
         <v>10</v>
@@ -10332,15 +10560,15 @@
         <v>0</v>
       </c>
       <c r="I241" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="242" spans="1:12">
       <c r="A242" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B242">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C242">
         <v>6</v>
@@ -10349,10 +10577,10 @@
         <v>2</v>
       </c>
       <c r="E242">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F242">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G242">
         <v>10</v>
@@ -10366,10 +10594,10 @@
     </row>
     <row r="243" spans="1:12">
       <c r="A243" t="s">
-        <v>279</v>
+        <v>125</v>
       </c>
       <c r="B243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C243">
         <v>6</v>
@@ -10378,7 +10606,7 @@
         <v>2</v>
       </c>
       <c r="E243">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F243">
         <v>7</v>
@@ -10390,15 +10618,15 @@
         <v>0</v>
       </c>
       <c r="I243" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
     </row>
     <row r="244" spans="1:12">
       <c r="A244" t="s">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="B244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C244">
         <v>6</v>
@@ -10407,13 +10635,13 @@
         <v>2</v>
       </c>
       <c r="E244">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F244">
         <v>7</v>
       </c>
       <c r="G244">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H244">
         <v>0</v>
@@ -10424,10 +10652,10 @@
     </row>
     <row r="245" spans="1:12">
       <c r="A245" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="B245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C245">
         <v>6</v>
@@ -10436,10 +10664,10 @@
         <v>2</v>
       </c>
       <c r="E245">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F245">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G245">
         <v>10</v>
@@ -10449,14 +10677,23 @@
       </c>
       <c r="I245" t="s">
         <v>57</v>
+      </c>
+      <c r="J245" t="s">
+        <v>154</v>
+      </c>
+      <c r="K245">
+        <v>1</v>
+      </c>
+      <c r="L245" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="246" spans="1:12">
       <c r="A246" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="B246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C246">
         <v>6</v>
@@ -10465,10 +10702,10 @@
         <v>2</v>
       </c>
       <c r="E246">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F246">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G246">
         <v>10</v>
@@ -10480,7 +10717,7 @@
         <v>57</v>
       </c>
       <c r="J246" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K246">
         <v>1</v>
@@ -10491,10 +10728,10 @@
     </row>
     <row r="247" spans="1:12">
       <c r="A247" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="B247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C247">
         <v>6</v>
@@ -10503,10 +10740,10 @@
         <v>2</v>
       </c>
       <c r="E247">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F247">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G247">
         <v>10</v>
@@ -10515,24 +10752,24 @@
         <v>0</v>
       </c>
       <c r="I247" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="J247" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K247">
         <v>1</v>
       </c>
       <c r="L247" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="248" spans="1:12">
       <c r="A248" t="s">
-        <v>292</v>
+        <v>217</v>
       </c>
       <c r="B248">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C248">
         <v>6</v>
@@ -10541,10 +10778,10 @@
         <v>2</v>
       </c>
       <c r="E248">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F248">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G248">
         <v>10</v>
@@ -10558,10 +10795,10 @@
     </row>
     <row r="249" spans="1:12">
       <c r="A249" t="s">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="B249">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C249">
         <v>6</v>
@@ -10570,7 +10807,7 @@
         <v>2</v>
       </c>
       <c r="E249">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F249">
         <v>10</v>
@@ -10583,29 +10820,38 @@
       </c>
       <c r="I249" t="s">
         <v>57</v>
+      </c>
+      <c r="J249" t="s">
+        <v>158</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="250" spans="1:12">
       <c r="A250" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="B250">
+        <v>5</v>
+      </c>
+      <c r="C250">
         <v>4</v>
       </c>
-      <c r="C250">
-        <v>6</v>
-      </c>
       <c r="D250">
         <v>2</v>
       </c>
       <c r="E250">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F250">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G250">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -10616,10 +10862,10 @@
     </row>
     <row r="251" spans="1:12">
       <c r="A251" t="s">
-        <v>232</v>
+        <v>130</v>
       </c>
       <c r="B251">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C251">
         <v>6</v>
@@ -10628,10 +10874,10 @@
         <v>2</v>
       </c>
       <c r="E251">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F251">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G251">
         <v>10</v>
@@ -10645,39 +10891,39 @@
     </row>
     <row r="252" spans="1:12">
       <c r="A252" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="B252">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C252">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D252">
         <v>2</v>
       </c>
       <c r="E252">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F252">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G252">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H252">
         <v>0</v>
       </c>
       <c r="I252" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>345</v>
+        <v>131</v>
       </c>
       <c r="B253">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C253">
         <v>6</v>
@@ -10686,27 +10932,36 @@
         <v>2</v>
       </c>
       <c r="E253">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F253">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G253">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H253">
         <v>0</v>
       </c>
       <c r="I253" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J253" t="s">
+        <v>343</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="254" spans="1:12">
       <c r="A254" t="s">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="B254">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C254">
         <v>6</v>
@@ -10715,10 +10970,10 @@
         <v>2</v>
       </c>
       <c r="E254">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F254">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G254">
         <v>10</v>
@@ -10727,15 +10982,15 @@
         <v>0</v>
       </c>
       <c r="I254" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255" spans="1:12">
       <c r="A255" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="B255">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C255">
         <v>6</v>
@@ -10744,7 +10999,7 @@
         <v>2</v>
       </c>
       <c r="E255">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F255">
         <v>7</v>
@@ -10761,19 +11016,19 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" t="s">
-        <v>335</v>
+        <v>132</v>
       </c>
       <c r="B256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C256">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D256">
         <v>2</v>
       </c>
       <c r="E256">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F256">
         <v>7</v>
@@ -10790,10 +11045,10 @@
     </row>
     <row r="257" spans="1:12">
       <c r="A257" t="s">
-        <v>189</v>
+        <v>303</v>
       </c>
       <c r="B257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C257">
         <v>6</v>
@@ -10802,10 +11057,10 @@
         <v>2</v>
       </c>
       <c r="E257">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F257">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G257">
         <v>10</v>
@@ -10815,23 +11070,14 @@
       </c>
       <c r="I257" t="s">
         <v>57</v>
-      </c>
-      <c r="J257" t="s">
-        <v>190</v>
-      </c>
-      <c r="K257">
-        <v>1</v>
-      </c>
-      <c r="L257" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="258" spans="1:12">
       <c r="A258" t="s">
-        <v>248</v>
+        <v>448</v>
       </c>
       <c r="B258">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C258">
         <v>6</v>
@@ -10840,27 +11086,36 @@
         <v>2</v>
       </c>
       <c r="E258">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F258">
         <v>10</v>
       </c>
       <c r="G258">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H258">
         <v>0</v>
       </c>
       <c r="I258" t="s">
         <v>57</v>
+      </c>
+      <c r="J258" t="s">
+        <v>408</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="259" spans="1:12">
       <c r="A259" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="B259">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C259">
         <v>6</v>
@@ -10869,7 +11124,7 @@
         <v>2</v>
       </c>
       <c r="E259">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F259">
         <v>7</v>
@@ -10881,21 +11136,12 @@
         <v>0</v>
       </c>
       <c r="I259" t="s">
-        <v>165</v>
-      </c>
-      <c r="J259" t="s">
-        <v>160</v>
-      </c>
-      <c r="K259">
-        <v>1</v>
-      </c>
-      <c r="L259" s="8" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260" spans="1:12">
       <c r="A260" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="B260">
         <v>4</v>
@@ -10910,7 +11156,7 @@
         <v>70</v>
       </c>
       <c r="F260">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G260">
         <v>10</v>
@@ -10924,7 +11170,7 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="B261">
         <v>4</v>
@@ -10939,7 +11185,7 @@
         <v>70</v>
       </c>
       <c r="F261">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G261">
         <v>10</v>
@@ -10948,21 +11194,12 @@
         <v>0</v>
       </c>
       <c r="I261" t="s">
-        <v>57</v>
-      </c>
-      <c r="J261" t="s">
-        <v>151</v>
-      </c>
-      <c r="K261">
-        <v>1</v>
-      </c>
-      <c r="L261" s="8" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" t="s">
-        <v>280</v>
+        <v>449</v>
       </c>
       <c r="B262">
         <v>4</v>
@@ -10991,7 +11228,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" t="s">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="B263">
         <v>4</v>
@@ -11006,7 +11243,7 @@
         <v>70</v>
       </c>
       <c r="F263">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G263">
         <v>10</v>
@@ -11015,12 +11252,21 @@
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>58</v>
+        <v>198</v>
+      </c>
+      <c r="J263" t="s">
+        <v>299</v>
+      </c>
+      <c r="K263">
+        <v>3</v>
+      </c>
+      <c r="L263" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="264" spans="1:12">
       <c r="A264" t="s">
-        <v>370</v>
+        <v>450</v>
       </c>
       <c r="B264">
         <v>4</v>
@@ -11035,10 +11281,10 @@
         <v>70</v>
       </c>
       <c r="F264">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G264">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H264">
         <v>0</v>
@@ -11049,7 +11295,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" t="s">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="B265">
         <v>4</v>
@@ -11064,21 +11310,21 @@
         <v>70</v>
       </c>
       <c r="F265">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G265">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H265">
         <v>0</v>
       </c>
       <c r="I265" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="266" spans="1:12">
       <c r="A266" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="B266">
         <v>4</v>
@@ -11093,7 +11339,7 @@
         <v>70</v>
       </c>
       <c r="F266">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G266">
         <v>10</v>
@@ -11102,12 +11348,21 @@
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="J266" t="s">
+        <v>159</v>
+      </c>
+      <c r="K266">
+        <v>3</v>
+      </c>
+      <c r="L266" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" t="s">
-        <v>74</v>
+        <v>322</v>
       </c>
       <c r="B267">
         <v>4</v>
@@ -11125,7 +11380,7 @@
         <v>10</v>
       </c>
       <c r="G267">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -11134,7 +11389,7 @@
         <v>57</v>
       </c>
       <c r="J267" t="s">
-        <v>156</v>
+        <v>347</v>
       </c>
       <c r="K267">
         <v>1</v>
@@ -11145,13 +11400,13 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="B268">
         <v>4</v>
       </c>
       <c r="C268">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -11163,27 +11418,18 @@
         <v>10</v>
       </c>
       <c r="G268">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H268">
         <v>0</v>
       </c>
       <c r="I268" t="s">
         <v>57</v>
-      </c>
-      <c r="J268" t="s">
-        <v>155</v>
-      </c>
-      <c r="K268">
-        <v>3</v>
-      </c>
-      <c r="L268" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="269" spans="1:12">
       <c r="A269" t="s">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="B269">
         <v>4</v>
@@ -11212,267 +11458,1490 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" t="s">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="B270">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E270">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F270">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H270">
         <v>0</v>
       </c>
       <c r="I270" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
     </row>
     <row r="271" spans="1:12">
       <c r="A271" t="s">
-        <v>264</v>
+        <v>64</v>
       </c>
       <c r="B271">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C271">
         <v>6</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E271">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H271">
         <v>0</v>
       </c>
       <c r="I271" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
     </row>
     <row r="272" spans="1:12">
       <c r="A272" t="s">
+        <v>201</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272">
+        <v>6</v>
+      </c>
+      <c r="D272">
+        <v>2</v>
+      </c>
+      <c r="E272">
+        <v>70</v>
+      </c>
+      <c r="F272">
+        <v>7</v>
+      </c>
+      <c r="G272">
+        <v>10</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12">
+      <c r="A273" t="s">
+        <v>211</v>
+      </c>
+      <c r="B273">
+        <v>4</v>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+      <c r="D273">
+        <v>2</v>
+      </c>
+      <c r="E273">
+        <v>70</v>
+      </c>
+      <c r="F273">
+        <v>10</v>
+      </c>
+      <c r="G273">
+        <v>7</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12">
+      <c r="A274" t="s">
+        <v>65</v>
+      </c>
+      <c r="B274">
+        <v>4</v>
+      </c>
+      <c r="C274">
+        <v>6</v>
+      </c>
+      <c r="D274">
+        <v>2</v>
+      </c>
+      <c r="E274">
+        <v>70</v>
+      </c>
+      <c r="F274">
+        <v>10</v>
+      </c>
+      <c r="G274">
+        <v>7</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12">
+      <c r="A275" t="s">
+        <v>239</v>
+      </c>
+      <c r="B275">
+        <v>4</v>
+      </c>
+      <c r="C275">
+        <v>6</v>
+      </c>
+      <c r="D275">
+        <v>2</v>
+      </c>
+      <c r="E275">
+        <v>70</v>
+      </c>
+      <c r="F275">
+        <v>7</v>
+      </c>
+      <c r="G275">
+        <v>10</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12">
+      <c r="A276" t="s">
+        <v>323</v>
+      </c>
+      <c r="B276">
+        <v>4</v>
+      </c>
+      <c r="C276">
+        <v>6</v>
+      </c>
+      <c r="D276">
+        <v>2</v>
+      </c>
+      <c r="E276">
+        <v>70</v>
+      </c>
+      <c r="F276">
+        <v>7</v>
+      </c>
+      <c r="G276">
+        <v>10</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12">
+      <c r="A277" t="s">
+        <v>346</v>
+      </c>
+      <c r="B277">
+        <v>4</v>
+      </c>
+      <c r="C277">
+        <v>6</v>
+      </c>
+      <c r="D277">
+        <v>2</v>
+      </c>
+      <c r="E277">
+        <v>70</v>
+      </c>
+      <c r="F277">
+        <v>7</v>
+      </c>
+      <c r="G277">
+        <v>10</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12">
+      <c r="A278" t="s">
+        <v>66</v>
+      </c>
+      <c r="B278">
+        <v>4</v>
+      </c>
+      <c r="C278">
+        <v>6</v>
+      </c>
+      <c r="D278">
+        <v>2</v>
+      </c>
+      <c r="E278">
+        <v>70</v>
+      </c>
+      <c r="F278">
+        <v>10</v>
+      </c>
+      <c r="G278">
+        <v>10</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>4</v>
+      </c>
+      <c r="C279">
+        <v>6</v>
+      </c>
+      <c r="D279">
+        <v>2</v>
+      </c>
+      <c r="E279">
+        <v>70</v>
+      </c>
+      <c r="F279">
+        <v>10</v>
+      </c>
+      <c r="G279">
+        <v>10</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>4</v>
+      </c>
+      <c r="C280">
+        <v>6</v>
+      </c>
+      <c r="D280">
+        <v>2</v>
+      </c>
+      <c r="E280">
+        <v>70</v>
+      </c>
+      <c r="F280">
+        <v>7</v>
+      </c>
+      <c r="G280">
+        <v>10</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12">
+      <c r="A281" t="s">
+        <v>451</v>
+      </c>
+      <c r="B281">
+        <v>4</v>
+      </c>
+      <c r="C281">
+        <v>6</v>
+      </c>
+      <c r="D281">
+        <v>2</v>
+      </c>
+      <c r="E281">
+        <v>70</v>
+      </c>
+      <c r="F281">
+        <v>7</v>
+      </c>
+      <c r="G281">
+        <v>10</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12">
+      <c r="A282" t="s">
+        <v>212</v>
+      </c>
+      <c r="B282">
+        <v>4</v>
+      </c>
+      <c r="C282">
+        <v>6</v>
+      </c>
+      <c r="D282">
+        <v>2</v>
+      </c>
+      <c r="E282">
+        <v>70</v>
+      </c>
+      <c r="F282">
+        <v>7</v>
+      </c>
+      <c r="G282">
+        <v>10</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12">
+      <c r="A283" t="s">
+        <v>71</v>
+      </c>
+      <c r="B283">
+        <v>4</v>
+      </c>
+      <c r="C283">
+        <v>6</v>
+      </c>
+      <c r="D283">
+        <v>2</v>
+      </c>
+      <c r="E283">
+        <v>70</v>
+      </c>
+      <c r="F283">
+        <v>7</v>
+      </c>
+      <c r="G283">
+        <v>10</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12">
+      <c r="A284" t="s">
+        <v>67</v>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
+      <c r="C284">
+        <v>6</v>
+      </c>
+      <c r="D284">
+        <v>2</v>
+      </c>
+      <c r="E284">
+        <v>70</v>
+      </c>
+      <c r="F284">
+        <v>7</v>
+      </c>
+      <c r="G284">
+        <v>10</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284" t="s">
+        <v>57</v>
+      </c>
+      <c r="J284" t="s">
+        <v>157</v>
+      </c>
+      <c r="K284">
+        <v>1</v>
+      </c>
+      <c r="L284" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12">
+      <c r="A285" t="s">
+        <v>68</v>
+      </c>
+      <c r="B285">
+        <v>4</v>
+      </c>
+      <c r="C285">
+        <v>6</v>
+      </c>
+      <c r="D285">
+        <v>2</v>
+      </c>
+      <c r="E285">
+        <v>70</v>
+      </c>
+      <c r="F285">
+        <v>7</v>
+      </c>
+      <c r="G285">
+        <v>10</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285" t="s">
+        <v>69</v>
+      </c>
+      <c r="J285" t="s">
+        <v>143</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12">
+      <c r="A286" t="s">
+        <v>452</v>
+      </c>
+      <c r="B286">
+        <v>4</v>
+      </c>
+      <c r="C286">
+        <v>6</v>
+      </c>
+      <c r="D286">
+        <v>2</v>
+      </c>
+      <c r="E286">
+        <v>70</v>
+      </c>
+      <c r="F286">
+        <v>7</v>
+      </c>
+      <c r="G286">
+        <v>7</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12">
+      <c r="A287" t="s">
+        <v>292</v>
+      </c>
+      <c r="B287">
+        <v>4</v>
+      </c>
+      <c r="C287">
+        <v>6</v>
+      </c>
+      <c r="D287">
+        <v>2</v>
+      </c>
+      <c r="E287">
+        <v>70</v>
+      </c>
+      <c r="F287">
+        <v>7</v>
+      </c>
+      <c r="G287">
+        <v>10</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12">
+      <c r="A288" t="s">
+        <v>234</v>
+      </c>
+      <c r="B288">
+        <v>4</v>
+      </c>
+      <c r="C288">
+        <v>6</v>
+      </c>
+      <c r="D288">
+        <v>2</v>
+      </c>
+      <c r="E288">
+        <v>70</v>
+      </c>
+      <c r="F288">
+        <v>10</v>
+      </c>
+      <c r="G288">
+        <v>7</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12">
+      <c r="A289" t="s">
+        <v>231</v>
+      </c>
+      <c r="B289">
+        <v>4</v>
+      </c>
+      <c r="C289">
+        <v>6</v>
+      </c>
+      <c r="D289">
+        <v>2</v>
+      </c>
+      <c r="E289">
+        <v>70</v>
+      </c>
+      <c r="F289">
+        <v>10</v>
+      </c>
+      <c r="G289">
+        <v>8</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12">
+      <c r="A290" t="s">
+        <v>232</v>
+      </c>
+      <c r="B290">
+        <v>4</v>
+      </c>
+      <c r="C290">
+        <v>6</v>
+      </c>
+      <c r="D290">
+        <v>2</v>
+      </c>
+      <c r="E290">
+        <v>70</v>
+      </c>
+      <c r="F290">
+        <v>7</v>
+      </c>
+      <c r="G290">
+        <v>10</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12">
+      <c r="A291" t="s">
+        <v>70</v>
+      </c>
+      <c r="B291">
+        <v>4</v>
+      </c>
+      <c r="C291">
+        <v>6</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291">
+        <v>70</v>
+      </c>
+      <c r="F291">
+        <v>10</v>
+      </c>
+      <c r="G291">
+        <v>10</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12">
+      <c r="A292" t="s">
+        <v>345</v>
+      </c>
+      <c r="B292">
+        <v>4</v>
+      </c>
+      <c r="C292">
+        <v>6</v>
+      </c>
+      <c r="D292">
+        <v>2</v>
+      </c>
+      <c r="E292">
+        <v>70</v>
+      </c>
+      <c r="F292">
+        <v>7</v>
+      </c>
+      <c r="G292">
+        <v>10</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12">
+      <c r="A293" t="s">
+        <v>321</v>
+      </c>
+      <c r="B293">
+        <v>4</v>
+      </c>
+      <c r="C293">
+        <v>6</v>
+      </c>
+      <c r="D293">
+        <v>2</v>
+      </c>
+      <c r="E293">
+        <v>70</v>
+      </c>
+      <c r="F293">
+        <v>10</v>
+      </c>
+      <c r="G293">
+        <v>10</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12">
+      <c r="A294" t="s">
+        <v>369</v>
+      </c>
+      <c r="B294">
+        <v>4</v>
+      </c>
+      <c r="C294">
+        <v>6</v>
+      </c>
+      <c r="D294">
+        <v>2</v>
+      </c>
+      <c r="E294">
+        <v>70</v>
+      </c>
+      <c r="F294">
+        <v>7</v>
+      </c>
+      <c r="G294">
+        <v>10</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12">
+      <c r="A295" t="s">
+        <v>335</v>
+      </c>
+      <c r="B295">
+        <v>4</v>
+      </c>
+      <c r="C295">
+        <v>6</v>
+      </c>
+      <c r="D295">
+        <v>2</v>
+      </c>
+      <c r="E295">
+        <v>70</v>
+      </c>
+      <c r="F295">
+        <v>7</v>
+      </c>
+      <c r="G295">
+        <v>10</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12">
+      <c r="A296" t="s">
+        <v>189</v>
+      </c>
+      <c r="B296">
+        <v>4</v>
+      </c>
+      <c r="C296">
+        <v>6</v>
+      </c>
+      <c r="D296">
+        <v>2</v>
+      </c>
+      <c r="E296">
+        <v>70</v>
+      </c>
+      <c r="F296">
+        <v>10</v>
+      </c>
+      <c r="G296">
+        <v>10</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296" t="s">
+        <v>57</v>
+      </c>
+      <c r="J296" t="s">
+        <v>190</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12">
+      <c r="A297" t="s">
+        <v>248</v>
+      </c>
+      <c r="B297">
+        <v>4</v>
+      </c>
+      <c r="C297">
+        <v>6</v>
+      </c>
+      <c r="D297">
+        <v>2</v>
+      </c>
+      <c r="E297">
+        <v>70</v>
+      </c>
+      <c r="F297">
+        <v>10</v>
+      </c>
+      <c r="G297">
+        <v>7</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12">
+      <c r="A298" t="s">
+        <v>72</v>
+      </c>
+      <c r="B298">
+        <v>4</v>
+      </c>
+      <c r="C298">
+        <v>6</v>
+      </c>
+      <c r="D298">
+        <v>2</v>
+      </c>
+      <c r="E298">
+        <v>70</v>
+      </c>
+      <c r="F298">
+        <v>7</v>
+      </c>
+      <c r="G298">
+        <v>10</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298" t="s">
+        <v>165</v>
+      </c>
+      <c r="J298" t="s">
+        <v>160</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
+      </c>
+      <c r="L298" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12">
+      <c r="A299" t="s">
+        <v>191</v>
+      </c>
+      <c r="B299">
+        <v>4</v>
+      </c>
+      <c r="C299">
+        <v>6</v>
+      </c>
+      <c r="D299">
+        <v>2</v>
+      </c>
+      <c r="E299">
+        <v>70</v>
+      </c>
+      <c r="F299">
+        <v>7</v>
+      </c>
+      <c r="G299">
+        <v>10</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12">
+      <c r="A300" t="s">
+        <v>73</v>
+      </c>
+      <c r="B300">
+        <v>4</v>
+      </c>
+      <c r="C300">
+        <v>6</v>
+      </c>
+      <c r="D300">
+        <v>2</v>
+      </c>
+      <c r="E300">
+        <v>70</v>
+      </c>
+      <c r="F300">
+        <v>10</v>
+      </c>
+      <c r="G300">
+        <v>10</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300" t="s">
+        <v>57</v>
+      </c>
+      <c r="J300" t="s">
+        <v>151</v>
+      </c>
+      <c r="K300">
+        <v>1</v>
+      </c>
+      <c r="L300" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12">
+      <c r="A301" t="s">
+        <v>280</v>
+      </c>
+      <c r="B301">
+        <v>4</v>
+      </c>
+      <c r="C301">
+        <v>6</v>
+      </c>
+      <c r="D301">
+        <v>2</v>
+      </c>
+      <c r="E301">
+        <v>70</v>
+      </c>
+      <c r="F301">
+        <v>7</v>
+      </c>
+      <c r="G301">
+        <v>10</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12">
+      <c r="A302" t="s">
+        <v>281</v>
+      </c>
+      <c r="B302">
+        <v>4</v>
+      </c>
+      <c r="C302">
+        <v>6</v>
+      </c>
+      <c r="D302">
+        <v>2</v>
+      </c>
+      <c r="E302">
+        <v>70</v>
+      </c>
+      <c r="F302">
+        <v>7</v>
+      </c>
+      <c r="G302">
+        <v>10</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12">
+      <c r="A303" t="s">
+        <v>370</v>
+      </c>
+      <c r="B303">
+        <v>4</v>
+      </c>
+      <c r="C303">
+        <v>6</v>
+      </c>
+      <c r="D303">
+        <v>2</v>
+      </c>
+      <c r="E303">
+        <v>70</v>
+      </c>
+      <c r="F303">
+        <v>7</v>
+      </c>
+      <c r="G303">
+        <v>7</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12">
+      <c r="A304" t="s">
+        <v>199</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304">
+        <v>6</v>
+      </c>
+      <c r="D304">
+        <v>2</v>
+      </c>
+      <c r="E304">
+        <v>70</v>
+      </c>
+      <c r="F304">
+        <v>10</v>
+      </c>
+      <c r="G304">
+        <v>7</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12">
+      <c r="A305" t="s">
+        <v>213</v>
+      </c>
+      <c r="B305">
+        <v>4</v>
+      </c>
+      <c r="C305">
+        <v>6</v>
+      </c>
+      <c r="D305">
+        <v>2</v>
+      </c>
+      <c r="E305">
+        <v>70</v>
+      </c>
+      <c r="F305">
+        <v>7</v>
+      </c>
+      <c r="G305">
+        <v>10</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12">
+      <c r="A306" t="s">
+        <v>74</v>
+      </c>
+      <c r="B306">
+        <v>4</v>
+      </c>
+      <c r="C306">
+        <v>6</v>
+      </c>
+      <c r="D306">
+        <v>2</v>
+      </c>
+      <c r="E306">
+        <v>70</v>
+      </c>
+      <c r="F306">
+        <v>10</v>
+      </c>
+      <c r="G306">
+        <v>10</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306" t="s">
+        <v>57</v>
+      </c>
+      <c r="J306" t="s">
+        <v>156</v>
+      </c>
+      <c r="K306">
+        <v>1</v>
+      </c>
+      <c r="L306" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12">
+      <c r="A307" t="s">
+        <v>75</v>
+      </c>
+      <c r="B307">
+        <v>4</v>
+      </c>
+      <c r="C307">
+        <v>6</v>
+      </c>
+      <c r="D307">
+        <v>2</v>
+      </c>
+      <c r="E307">
+        <v>70</v>
+      </c>
+      <c r="F307">
+        <v>10</v>
+      </c>
+      <c r="G307">
+        <v>10</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307" t="s">
+        <v>57</v>
+      </c>
+      <c r="J307" t="s">
+        <v>155</v>
+      </c>
+      <c r="K307">
+        <v>3</v>
+      </c>
+      <c r="L307" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12">
+      <c r="A308" t="s">
+        <v>76</v>
+      </c>
+      <c r="B308">
+        <v>4</v>
+      </c>
+      <c r="C308">
+        <v>6</v>
+      </c>
+      <c r="D308">
+        <v>2</v>
+      </c>
+      <c r="E308">
+        <v>70</v>
+      </c>
+      <c r="F308">
+        <v>7</v>
+      </c>
+      <c r="G308">
+        <v>10</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12">
+      <c r="A309" t="s">
+        <v>453</v>
+      </c>
+      <c r="B309">
+        <v>4</v>
+      </c>
+      <c r="C309">
+        <v>6</v>
+      </c>
+      <c r="D309">
+        <v>2</v>
+      </c>
+      <c r="E309">
+        <v>70</v>
+      </c>
+      <c r="F309">
+        <v>7</v>
+      </c>
+      <c r="G309">
+        <v>10</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12">
+      <c r="A310" t="s">
+        <v>409</v>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>30</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12">
+      <c r="A311" t="s">
+        <v>264</v>
+      </c>
+      <c r="B311">
+        <v>1</v>
+      </c>
+      <c r="C311">
+        <v>6</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>30</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12">
+      <c r="A312" t="s">
         <v>283</v>
       </c>
-      <c r="B272">
+      <c r="B312">
         <v>1</v>
       </c>
-      <c r="C272">
-        <v>6</v>
-      </c>
-      <c r="D272">
-        <v>0</v>
-      </c>
-      <c r="E272">
+      <c r="C312">
+        <v>6</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
         <v>30</v>
       </c>
-      <c r="F272">
-        <v>0</v>
-      </c>
-      <c r="G272">
-        <v>0</v>
-      </c>
-      <c r="H272">
-        <v>0</v>
-      </c>
-      <c r="I272" t="s">
+      <c r="F312">
+        <v>0</v>
+      </c>
+      <c r="G312">
+        <v>0</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
-      <c r="A273" t="s">
+    <row r="313" spans="1:12">
+      <c r="A313" t="s">
         <v>265</v>
       </c>
-      <c r="B273">
+      <c r="B313">
         <v>1</v>
       </c>
-      <c r="C273">
-        <v>6</v>
-      </c>
-      <c r="D273">
-        <v>0</v>
-      </c>
-      <c r="E273">
+      <c r="C313">
+        <v>6</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
         <v>30</v>
       </c>
-      <c r="F273">
-        <v>0</v>
-      </c>
-      <c r="G273">
-        <v>0</v>
-      </c>
-      <c r="H273">
-        <v>0</v>
-      </c>
-      <c r="I273" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9">
-      <c r="A274" t="s">
+      <c r="F313">
+        <v>0</v>
+      </c>
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12">
+      <c r="A314" t="s">
         <v>266</v>
       </c>
-      <c r="B274">
+      <c r="B314">
         <v>1</v>
       </c>
-      <c r="C274">
-        <v>6</v>
-      </c>
-      <c r="D274">
-        <v>0</v>
-      </c>
-      <c r="E274">
+      <c r="C314">
+        <v>6</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
         <v>30</v>
       </c>
-      <c r="F274">
-        <v>0</v>
-      </c>
-      <c r="G274">
-        <v>0</v>
-      </c>
-      <c r="H274">
-        <v>0</v>
-      </c>
-      <c r="I274" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9">
-      <c r="A275" t="s">
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314">
+        <v>0</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12">
+      <c r="A315" t="s">
         <v>267</v>
       </c>
-      <c r="B275">
+      <c r="B315">
         <v>1</v>
       </c>
-      <c r="C275">
-        <v>6</v>
-      </c>
-      <c r="D275">
-        <v>0</v>
-      </c>
-      <c r="E275">
+      <c r="C315">
+        <v>6</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
         <v>30</v>
       </c>
-      <c r="F275">
-        <v>0</v>
-      </c>
-      <c r="G275">
-        <v>0</v>
-      </c>
-      <c r="H275">
-        <v>0</v>
-      </c>
-      <c r="I275" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9">
-      <c r="A276" t="s">
+      <c r="F315">
+        <v>0</v>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12">
+      <c r="A316" t="s">
         <v>366</v>
       </c>
-      <c r="B276">
+      <c r="B316">
         <v>1</v>
       </c>
-      <c r="C276">
-        <v>6</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-      <c r="E276">
+      <c r="C316">
+        <v>6</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
         <v>30</v>
       </c>
-      <c r="F276">
-        <v>0</v>
-      </c>
-      <c r="G276">
-        <v>0</v>
-      </c>
-      <c r="H276">
-        <v>0</v>
-      </c>
-      <c r="I276" t="s">
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
-      <c r="A277" t="s">
+    <row r="317" spans="1:12">
+      <c r="A317" t="s">
         <v>268</v>
       </c>
-      <c r="B277">
+      <c r="B317">
         <v>1</v>
       </c>
-      <c r="C277">
-        <v>6</v>
-      </c>
-      <c r="D277">
-        <v>0</v>
-      </c>
-      <c r="E277">
+      <c r="C317">
+        <v>6</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
         <v>30</v>
       </c>
-      <c r="F277">
-        <v>0</v>
-      </c>
-      <c r="G277">
-        <v>0</v>
-      </c>
-      <c r="H277">
-        <v>0</v>
-      </c>
-      <c r="I277" t="s">
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>0</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
-      <c r="A278" t="s">
+    <row r="318" spans="1:12">
+      <c r="A318" t="s">
         <v>293</v>
       </c>
-      <c r="B278">
+      <c r="B318">
         <v>1</v>
       </c>
-      <c r="C278">
-        <v>6</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278">
+      <c r="C318">
+        <v>6</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
         <v>30</v>
       </c>
-      <c r="F278">
-        <v>0</v>
-      </c>
-      <c r="G278">
-        <v>0</v>
-      </c>
-      <c r="H278">
-        <v>0</v>
-      </c>
-      <c r="I278" t="s">
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318" t="s">
         <v>273</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L269" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:L308" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
     <filterColumn colId="6" showButton="0"/>
@@ -11484,25 +12953,18 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I279:I306" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I319:I346" xr:uid="{A8166145-CD83-4526-BE5E-2B372ACB9134}">
       <formula1>"elite1,elite2,skin1,skin2,skin3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L312:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L352:L1048576" xr:uid="{35D8C5A6-1D48-45E0-94E2-28AE42BE7947}">
       <formula1>"蓝色,绿色,灰色,红色,金色"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1048576" xr:uid="{067929F4-68AD-4FCF-9645-B8AA87BCECB2}">
       <formula1>0</formula1>
       <formula2>90</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L311" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
-      <formula1>"blue,green,grey,red,yellow"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I278" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I318" xr:uid="{368FC40C-689B-46DB-A600-7962187E38F1}">
       <formula1>"elite0,elite1,elite2,skin1,skin2,skin3"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">
-      <formula1>1</formula1>
-      <formula2>3</formula2>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C1048576" xr:uid="{84D7772C-943A-4833-B43B-BB959E902FB7}">
       <formula1>1</formula1>
@@ -11516,6 +12978,13 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L351" xr:uid="{4B8A5B42-2203-4F2F-B5D5-3836403806BE}">
+      <formula1>"blue,green,grey,red,yellow"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1048576" xr:uid="{7C51FEFB-34AE-4B58-A0CE-D8B56128B1B0}">
+      <formula1>1</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
